--- a/Results/Phase 2/Hydrogen/hydrogen ozone depletion results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ozone depletion results.xlsx
@@ -886,7 +886,7 @@
         <v>6.899535759914995e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>5.87579820828155e-06</v>
+        <v>6.899535759915147e-08</v>
       </c>
       <c r="O5" t="n">
         <v>6.899535759915147e-08</v>
@@ -974,7 +974,7 @@
         <v>1.198444563299333e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>5.87579820828155e-06</v>
+        <v>8.847596240831702e-08</v>
       </c>
       <c r="O6" t="n">
         <v>8.847521522923647e-08</v>
@@ -1062,7 +1062,7 @@
         <v>9.454875777333441e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.87579820828155e-06</v>
+        <v>9.454875777333441e-08</v>
       </c>
       <c r="O7" t="n">
         <v>9.454715087182779e-08</v>
@@ -1150,7 +1150,7 @@
         <v>1.710879207636225e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>5.87579820828155e-06</v>
+        <v>1.35280465334711e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.451206649172888e-07</v>
@@ -1238,7 +1238,7 @@
         <v>4.143745793809697e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>5.87579820828155e-06</v>
+        <v>4.143745793809697e-07</v>
       </c>
       <c r="O9" t="n">
         <v>4.403772855923548e-07</v>
@@ -1922,7 +1922,7 @@
         <v>5.428269933821505e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.467289608181302e-07</v>
+        <v>5.428269933821495e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.428269933821495e-08</v>
@@ -2010,7 +2010,7 @@
         <v>6.666704457955164e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.467289608181302e-07</v>
+        <v>6.667091211380388e-08</v>
       </c>
       <c r="O6" t="n">
         <v>9.17176812630588e-08</v>
@@ -2098,7 +2098,7 @@
         <v>6.976299277626563e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.467289608181302e-07</v>
+        <v>6.976299277626563e-08</v>
       </c>
       <c r="O7" t="n">
         <v>6.9762430866297e-08</v>
@@ -2186,7 +2186,7 @@
         <v>1.164468831077559e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>7.467289608181302e-07</v>
+        <v>9.49995654407793e-08</v>
       </c>
       <c r="O8" t="n">
         <v>1.008934745210406e-07</v>
@@ -2274,7 +2274,7 @@
         <v>2.578431980003786e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>7.467289608181302e-07</v>
+        <v>2.578431980003786e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.731074524093655e-07</v>
@@ -2958,7 +2958,7 @@
         <v>6.438398587035511e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.478799437613898e-06</v>
+        <v>6.43839858703551e-08</v>
       </c>
       <c r="O5" t="n">
         <v>6.43839858703551e-08</v>
@@ -3046,7 +3046,7 @@
         <v>1.087270241369904e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.478799437613898e-06</v>
+        <v>8.165622540856523e-08</v>
       </c>
       <c r="O6" t="n">
         <v>8.183522006918048e-08</v>
@@ -3134,7 +3134,7 @@
         <v>8.590795717319312e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.478799437613898e-06</v>
+        <v>8.590795717319312e-08</v>
       </c>
       <c r="O7" t="n">
         <v>8.590650816024526e-08</v>
@@ -3222,7 +3222,7 @@
         <v>1.507753525386225e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.478799437613898e-06</v>
+        <v>1.205315667628557e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.288428216294085e-07</v>
@@ -3310,7 +3310,7 @@
         <v>3.393750674475517e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.478799437613898e-06</v>
+        <v>3.393750674475517e-07</v>
       </c>
       <c r="O9" t="n">
         <v>3.601252330631332e-07</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.531795218576782e-07</v>
+        <v>9.531795218576768e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.580192756650447e-07</v>
+        <v>9.58019275665044e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.564574876411854e-07</v>
+        <v>9.564574876411844e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.531157452608473e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.541312690000774e-07</v>
+        <v>9.541312690000772e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.534298307058823e-07</v>
+        <v>9.534298307058822e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.564065465958492e-07</v>
+        <v>9.564065465958484e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.545350301783796e-07</v>
+        <v>9.545350301783789e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.550412667072928e-07</v>
+        <v>9.550412667072924e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.536627759873907e-07</v>
+        <v>9.536627759873904e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.529444541826137e-07</v>
+        <v>9.52944454182613e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.539180913647243e-07</v>
+        <v>9.539180913647232e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.595922589912833e-07</v>
+        <v>9.595922589912826e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.53851511022431e-07</v>
+        <v>9.538515110224295e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.549478486447069e-07</v>
+        <v>9.549478486447065e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.555575110528012e-07</v>
+        <v>9.555575110528004e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.554578044936284e-07</v>
+        <v>9.554578044936278e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.548982969589911e-07</v>
+        <v>9.548982969589897e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.540695825292568e-07</v>
+        <v>9.540695825292553e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.550301437794665e-07</v>
+        <v>9.550301437794651e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.189811989769136e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.681219046009357e-07</v>
+        <v>9.681219046009351e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.554533720341338e-07</v>
+        <v>9.554533720341336e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>9.551715727920277e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.546606530849479e-07</v>
+        <v>9.546606530849469e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.545220325912568e-07</v>
+        <v>9.545220325912565e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.537043917267772e-07</v>
+        <v>9.537043917267774e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.551865896961908e-06</v>
+        <v>1.55186589696191e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.676031866292432e-07</v>
+        <v>9.676031866292421e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.206289476249775e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.67563189462688e-07</v>
+        <v>9.675631894626863e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.976754268362272e-07</v>
+        <v>1.976754268362248e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397472425441017e-06</v>
+        <v>1.397472425441015e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.072138591869943e-06</v>
+        <v>1.072138591869942e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.159238025284089e-07</v>
+        <v>9.159238025284064e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.610932083405744e-07</v>
+        <v>4.610932083405703e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.582649637088318e-07</v>
+        <v>2.582649637088321e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.110489054387523e-06</v>
+        <v>1.110489054387517e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.752572787560655e-07</v>
+        <v>5.752572787560611e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.590069211311644e-07</v>
+        <v>6.590069211311626e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.241666448052467e-07</v>
+        <v>3.241666448052443e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44604876185509e-07</v>
+        <v>1.446048761855056e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.12314407704835e-07</v>
+        <v>4.123144077048299e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>1.864463093171685e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>3.473651252284029e-07</v>
+        <v>3.473651252283997e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>6.130317828566903e-07</v>
+        <v>6.130317828566837e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.073006724415999e-07</v>
+        <v>8.07300672441596e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.337885574451144e-07</v>
+        <v>8.337885574451121e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>6.066231098611788e-07</v>
+        <v>6.066231098611759e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>4.483967345026878e-07</v>
+        <v>4.483967345026864e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.520945191815764e-07</v>
+        <v>6.52094519181583e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>5.700074716763317e-07</v>
+        <v>5.700074716763331e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.99598749826168e-06</v>
+        <v>3.995987498261675e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>7.984906456636305e-07</v>
+        <v>7.984906456636303e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.064484100591162e-07</v>
+        <v>7.064484100591137e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.280791573072959e-07</v>
+        <v>5.280791573072926e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.462523766728895e-07</v>
+        <v>5.46252376672886e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.680690971429606e-07</v>
+        <v>3.680690971429589e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7657501195493e-08</v>
+        <v>5.765750119549128e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.813432640068294e-08</v>
+        <v>5.813432640068057e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.765750119549396e-08</v>
+        <v>5.76575011954908e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>5.694670503484667e-08</v>
+        <v>5.694670503484461e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>6.082960039356102e-08</v>
+        <v>6.082960039356082e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>5.7657501195493e-08</v>
+        <v>5.765750119549128e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.694670503484667e-08</v>
+        <v>5.694670503484461e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.765750119549404e-08</v>
+        <v>5.765750119549065e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.765750119549312e-08</v>
+        <v>5.765750119549112e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.524543562746101e-08</v>
+        <v>9.524543562745572e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.572226083264912e-08</v>
+        <v>9.572226083264607e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.524543562746101e-08</v>
+        <v>9.524543562745572e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>7.253312914336188e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>9.920490541070679e-08</v>
+        <v>9.920490541070397e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.913724049047678e-08</v>
+        <v>9.913724049047469e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>9.841753482552787e-08</v>
+        <v>9.841753482552636e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>9.922750468071074e-08</v>
+        <v>9.922750468070769e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.275151336712346e-08</v>
+        <v>7.275151336711977e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.391100359308317e-08</v>
+        <v>7.391100359308071e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.524543562746104e-08</v>
+        <v>9.524543562745584e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.26612333955787e-08</v>
+        <v>7.266123339557703e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.505338869890087e-08</v>
+        <v>7.505338869889888e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.553021390409318e-08</v>
+        <v>7.553021390408897e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.505338869890087e-08</v>
+        <v>7.505338869889888e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>7.505257123856489e-08</v>
+        <v>7.505257123856157e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>7.505257123856489e-08</v>
+        <v>7.505257123856157e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>7.480647284547237e-08</v>
+        <v>7.480647284546938e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>7.822548789697067e-08</v>
+        <v>7.822548789696924e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.505338869890087e-08</v>
+        <v>7.505338869889888e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.505338869890053e-08</v>
+        <v>7.505338869889879e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.634915099442338e-08</v>
+        <v>9.634915099442237e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.110641376785522e-07</v>
+        <v>1.110641376785492e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.012524200894155e-07</v>
+        <v>1.012524200894133e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.343493949911235e-07</v>
+        <v>1.343493949911209e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.28299897573424e-07</v>
+        <v>1.282998975734226e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.278230723682363e-07</v>
+        <v>1.278230723682318e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.278230723684708e-07</v>
+        <v>1.278230723684685e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>1.034255178058071e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>1.101301775897321e-07</v>
+        <v>1.101301775897279e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>1.084867034745396e-07</v>
+        <v>1.084867034745355e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.016380711293848e-08</v>
+        <v>9.016380711293619e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.122703511519106e-07</v>
+        <v>1.12270351151909e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.221825154144339e-07</v>
+        <v>1.221825154144331e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.278292577983491e-07</v>
+        <v>1.278292577983468e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.304845448687756e-08</v>
+        <v>9.304845448687571e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.587906091757346e-07</v>
+        <v>1.587906091757325e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.576450675424476e-08</v>
+        <v>9.576450675424445e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.27823072368236e-07</v>
+        <v>1.278230723682319e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.607002149599119e-07</v>
+        <v>1.607002149599075e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.311305662754724e-07</v>
+        <v>2.311305662754682e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>2.703396833691401e-07</v>
+        <v>2.703396833691378e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6459607901424e-07</v>
+        <v>1.645960790142377e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.821041871491798e-07</v>
+        <v>2.821041871491771e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82580996691893e-07</v>
+        <v>2.825809966918912e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867009e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.86446309317169e-06</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>2.989967783624588e-07</v>
+        <v>2.98996778362456e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>3.026706271232954e-07</v>
+        <v>3.026706271232938e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.821041871491798e-07</v>
+        <v>2.821041871491771e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>3.44098729868351e-07</v>
+        <v>3.440987298683508e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867009e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.513716265135557e-07</v>
+        <v>2.513716265135526e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.821041714867039e-07</v>
+        <v>2.821041714867007e-07</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.640622453070824e-07</v>
+        <v>9.64062245307081e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>9.357304804225092e-07</v>
+        <v>9.357304804225093e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>9.44915591782213e-07</v>
+        <v>9.449155917822131e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>1.531684343761014e-06</v>
+        <v>1.531684343761015e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>9.585855806739475e-07</v>
+        <v>9.585855806739469e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>9.625758969065541e-07</v>
+        <v>9.625758969065524e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>9.453647881173049e-07</v>
+        <v>9.453647881173044e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>9.561977868781858e-07</v>
+        <v>9.561977868781841e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>9.533833028259503e-07</v>
+        <v>9.533833028259495e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>9.612767853975267e-07</v>
+        <v>9.612767853975259e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>9.654739813189812e-07</v>
+        <v>9.654739813189806e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>9.598197339233142e-07</v>
+        <v>9.598197339233131e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>9.263800153365454e-07</v>
+        <v>9.263800153365452e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>9.600562846923988e-07</v>
+        <v>9.600562846923986e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>9.535143995589083e-07</v>
+        <v>9.535143995589073e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.501427681422227e-07</v>
+        <v>9.501427681422216e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>9.508374850235598e-07</v>
+        <v>9.508374850235586e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>9.538793744029975e-07</v>
+        <v>9.538793744029969e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>9.589083286334949e-07</v>
+        <v>9.589083286334927e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>9.531293116656388e-07</v>
+        <v>9.531293116656386e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>1.193047443933629e-06</v>
+        <v>1.193047443933628e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>8.759005542850521e-07</v>
+        <v>8.759005542850517e-07</v>
       </c>
       <c r="X10" t="n">
-        <v>9.507810852584625e-07</v>
+        <v>9.507810852584616e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.523577057159941e-07</v>
+        <v>9.523577057159927e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.552643933800197e-07</v>
+        <v>9.552643933800189e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.561759349870814e-07</v>
+        <v>9.561759349870801e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.610434243378166e-07</v>
+        <v>9.610434243378155e-07</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.515865811100303e-07</v>
+        <v>9.515865811100301e-07</v>
       </c>
       <c r="C11" t="n">
-        <v>9.435352916069396e-07</v>
+        <v>9.435352916069389e-07</v>
       </c>
       <c r="D11" t="n">
-        <v>9.46152758522959e-07</v>
+        <v>9.461527585229582e-07</v>
       </c>
       <c r="E11" t="n">
-        <v>1.521974781587272e-06</v>
+        <v>1.521974781587271e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>9.500464283912588e-07</v>
+        <v>9.500464283912596e-07</v>
       </c>
       <c r="G11" t="n">
         <v>9.511605966992827e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>9.463062032415917e-07</v>
+        <v>9.463062032415912e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>9.493637357830428e-07</v>
+        <v>9.493637357830417e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>9.485711742607131e-07</v>
+        <v>9.485711742607126e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>9.508024421041617e-07</v>
+        <v>9.508024421041607e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>9.519938578193159e-07</v>
+        <v>9.519938578193154e-07</v>
       </c>
       <c r="M11" t="n">
-        <v>9.503947944173808e-07</v>
+        <v>9.503947944173795e-07</v>
       </c>
       <c r="N11" t="n">
         <v>9.408537835208999e-07</v>
       </c>
       <c r="O11" t="n">
-        <v>9.504358454288625e-07</v>
+        <v>9.50435845428863e-07</v>
       </c>
       <c r="P11" t="n">
-        <v>9.485556044676508e-07</v>
+        <v>9.485556044676492e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.476311638364001e-07</v>
+        <v>9.476311638363998e-07</v>
       </c>
       <c r="R11" t="n">
-        <v>9.478475556721666e-07</v>
+        <v>9.478475556721663e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>9.486721174991013e-07</v>
+        <v>9.486721174991006e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>9.501315932705681e-07</v>
+        <v>9.501315932705672e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>9.484626833837698e-07</v>
+        <v>9.484626833837689e-07</v>
       </c>
       <c r="V11" t="n">
-        <v>1.183786822865435e-06</v>
+        <v>1.183786822865436e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>9.26415113483625e-07</v>
+        <v>9.264151134836239e-07</v>
       </c>
       <c r="X11" t="n">
-        <v>9.478174611398183e-07</v>
+        <v>9.478174611398185e-07</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.482530292302805e-07</v>
+        <v>9.482530292302797e-07</v>
       </c>
       <c r="Z11" t="n">
         <v>9.490646616733959e-07</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.493407955158294e-07</v>
+        <v>9.493407955158293e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.507378778177023e-07</v>
+        <v>9.507378778177019e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.504461641586005e-07</v>
+        <v>9.504461641586023e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.556305858629168e-07</v>
+        <v>9.556305858629177e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.509494029854771e-07</v>
+        <v>9.509494029854793e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.528139211321621e-06</v>
+        <v>1.528139211321622e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.516320842615009e-07</v>
+        <v>9.516320842615023e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.507197419572598e-07</v>
+        <v>9.507197419572633e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.53180724452033e-07</v>
+        <v>9.531807244520338e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.507336228929849e-07</v>
+        <v>9.50733622892987e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.519773132698751e-07</v>
+        <v>9.519773132698769e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.504111673483445e-07</v>
+        <v>9.504111673483465e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.506027504257537e-07</v>
+        <v>9.506027504257542e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.509862619250294e-07</v>
+        <v>9.509862619250311e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.548550468634242e-07</v>
+        <v>9.548550468634268e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.505529727792833e-07</v>
+        <v>9.50552972779285e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.519168943088804e-07</v>
+        <v>9.519168943088815e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.523832370768244e-07</v>
+        <v>9.523832370768255e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.522586565932676e-07</v>
+        <v>9.522586565932678e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.518549053616756e-07</v>
+        <v>9.518549053616789e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.512070811403898e-07</v>
+        <v>9.512070811403917e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.531863903548162e-07</v>
+        <v>9.531863903548185e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.187015319351124e-06</v>
+        <v>1.187015319351125e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.639014264440052e-07</v>
+        <v>9.639014264440065e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.518348187128593e-07</v>
+        <v>9.518348187128608e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.51457181607787e-07</v>
+        <v>9.51457181607788e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.511750955750175e-07</v>
+        <v>9.511750955750187e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.520290368923659e-07</v>
+        <v>9.520290368923671e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.506013115249699e-07</v>
+        <v>9.506013115249724e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5501553687774e-06</v>
+        <v>1.550155368777403e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.646608263943938e-07</v>
+        <v>9.646608263943951e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.203208816387313e-06</v>
+        <v>1.203208816387312e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.646138578383342e-07</v>
+        <v>9.646138578383367e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.395551426867426e-07</v>
+        <v>2.395551426867479e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.516453659292817e-06</v>
+        <v>1.516453659292819e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>3.850550247946178e-07</v>
+        <v>3.850550247946304e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.577592810431845e-07</v>
+        <v>5.577592810431889e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.668657947153529e-07</v>
+        <v>5.668657947153543e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.037908494301602e-07</v>
+        <v>3.037908494301639e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02973962472561e-06</v>
+        <v>1.029739624725616e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>3.38039969720836e-07</v>
+        <v>3.380399697208389e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.166890099901348e-07</v>
+        <v>6.166890099901333e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.460063515938043e-07</v>
+        <v>2.460063515938072e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.862465172708678e-07</v>
+        <v>2.862465172708696e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.006526722443973e-07</v>
+        <v>4.006526722443976e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>1.399695324057151e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>2.623184851036292e-07</v>
+        <v>2.623184851036317e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.720748407511246e-07</v>
+        <v>5.720748407511238e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.271046145594555e-07</v>
+        <v>7.271046145594574e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>7.587820779859614e-07</v>
+        <v>7.587820779859674e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.712077251297899e-07</v>
+        <v>5.712077251297974e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>4.646587979068948e-07</v>
+        <v>4.646587979069007e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>8.857923428824056e-07</v>
+        <v>8.857923428824094e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.208873975270584e-07</v>
+        <v>6.208873975270596e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.673072986763812e-06</v>
+        <v>3.673072986763809e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>6.030395788213384e-07</v>
+        <v>6.030395788213397e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.139676838241141e-07</v>
+        <v>5.139676838241117e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.868836969379456e-07</v>
+        <v>3.86883696937951e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.579283416690975e-07</v>
+        <v>6.579283416691015e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.151257877218232e-07</v>
+        <v>3.151257877218257e-07</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.457982896160677e-08</v>
+        <v>5.457982896161035e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.505645181372108e-08</v>
+        <v>5.505645181372333e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.457982896160675e-08</v>
+        <v>5.457982896161132e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>5.188471421585246e-08</v>
+        <v>5.188471421585654e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>5.775047069304492e-08</v>
+        <v>5.775047069304495e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>5.457982896160677e-08</v>
+        <v>5.45798289616081e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.188471421585246e-08</v>
+        <v>5.188471421585654e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.457982896160633e-08</v>
+        <v>5.457982896161103e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.457982896160589e-08</v>
+        <v>5.457982896160818e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.028247528793613e-08</v>
+        <v>9.028247528793672e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>6.875050618871531e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.89001167681667e-08</v>
+        <v>6.890011676817202e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.377578457642322e-08</v>
+        <v>9.377578457642629e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>7.194438647213927e-08</v>
+        <v>7.194438647213842e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.112317979240182e-08</v>
+        <v>7.112317979240329e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.00048011182313e-08</v>
+        <v>7.000480111823355e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.877374474070259e-08</v>
+        <v>6.877374474070265e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.980585243582007e-08</v>
+        <v>8.980585243582841e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.881167650497734e-08</v>
+        <v>6.881167650498252e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.06122576805262e-08</v>
+        <v>7.061225768053047e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.108888053264049e-08</v>
+        <v>7.108888053264249e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.06122576805262e-08</v>
+        <v>7.061225768053047e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>7.06118608536694e-08</v>
+        <v>7.061186085367299e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>7.06118608536694e-08</v>
+        <v>7.061186085367299e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.977314863536777e-08</v>
+        <v>6.977314863536928e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>7.378289941196419e-08</v>
+        <v>7.378289941196405e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.06122576805262e-08</v>
+        <v>7.061225768053047e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.06122576805254e-08</v>
+        <v>7.061225768053023e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.081017963164723e-08</v>
+        <v>9.081017963164892e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.044615545942328e-07</v>
+        <v>1.044615545942359e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.535903627779883e-08</v>
+        <v>9.535903627780079e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.260637337575421e-07</v>
+        <v>1.260637337575454e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.204857621216389e-07</v>
+        <v>1.204857621216399e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.200091392695238e-07</v>
+        <v>1.200091392695277e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.200091392697677e-07</v>
+        <v>1.20009139269771e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>9.737506064886297e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>1.035951019391913e-07</v>
+        <v>1.035951019391954e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>1.02070419525969e-07</v>
+        <v>1.020704195259734e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.507191765083879e-08</v>
+        <v>8.507191765084218e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.05107535354265e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.144823545756012e-07</v>
+        <v>1.144823545756011e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.20014877618444e-07</v>
+        <v>1.200148776184465e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>8.774806026985441e-08</v>
+        <v>8.774806026985885e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.479290711720976e-07</v>
+        <v>1.479290711721016e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.026779397236882e-08</v>
+        <v>9.02677939723734e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.200091392695235e-07</v>
+        <v>1.200091392695274e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.505098941120846e-07</v>
+        <v>1.505098941120868e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.10749484249483e-07</v>
+        <v>2.107494842494855e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>2.460396248338777e-07</v>
+        <v>2.460396248338828e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>1.508651618468582e-07</v>
+        <v>1.50865161846863e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.566282588832374e-07</v>
+        <v>2.566282588832384e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>2.571048694935338e-07</v>
+        <v>2.571048694935339e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.566282466414182e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.399695324057143e-06</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>2.718324247237249e-07</v>
+        <v>2.718324247237291e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.751390699344824e-07</v>
+        <v>2.751390699344831e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.566282588832374e-07</v>
+        <v>2.566282588832384e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>3.127420054575399e-07</v>
+        <v>3.127420054575391e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>2.566282466414182e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.289674374788997e-07</v>
+        <v>2.28967437478902e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.566282466414181e-07</v>
+        <v>2.566282466414216e-07</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.599358566476532e-07</v>
+        <v>9.59935856647656e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>9.295996264200408e-07</v>
+        <v>9.295996264200426e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>9.570603761990281e-07</v>
+        <v>9.570603761990317e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>1.537697015147957e-06</v>
+        <v>1.53769701514796e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>9.531179847684562e-07</v>
+        <v>9.531179847684593e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>9.583118081358065e-07</v>
+        <v>9.583118081358072e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>9.441295065539462e-07</v>
+        <v>9.44129506553948e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>9.583361122172351e-07</v>
+        <v>9.583361122172359e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>9.512692987633768e-07</v>
+        <v>9.512692987633782e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>9.602068520078639e-07</v>
+        <v>9.60206852007866e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>9.590395806034674e-07</v>
+        <v>9.590395806034699e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>9.568740063111074e-07</v>
+        <v>9.5687400631111e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>9.340541472709835e-07</v>
+        <v>9.34054147270985e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>9.592946332989677e-07</v>
+        <v>9.592946332989689e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>9.511596399101534e-07</v>
+        <v>9.511596399101546e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.486208250196618e-07</v>
+        <v>9.486208250196634e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>9.494514132968289e-07</v>
+        <v>9.494514132968306e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>9.515953688165425e-07</v>
+        <v>9.515953688165451e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>9.555567808791191e-07</v>
+        <v>9.555567808791208e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>9.437446911294656e-07</v>
+        <v>9.437446911294683e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>1.188401598831823e-06</v>
+        <v>1.188401598831822e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>8.805604472092958e-07</v>
+        <v>8.805604472092976e-07</v>
       </c>
       <c r="X10" t="n">
-        <v>9.518617546578934e-07</v>
+        <v>9.518617546578958e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.540232207206373e-07</v>
+        <v>9.540232207206394e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.55609317873107e-07</v>
+        <v>9.556093178731093e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.506423708092603e-07</v>
+        <v>9.506423708092613e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.591005894820964e-07</v>
+        <v>9.591005894820985e-07</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.48317658708934e-07</v>
+        <v>9.483176587089355e-07</v>
       </c>
       <c r="C11" t="n">
-        <v>9.396989989838583e-07</v>
+        <v>9.396989989838597e-07</v>
       </c>
       <c r="D11" t="n">
-        <v>9.475125447680754e-07</v>
+        <v>9.475125447680773e-07</v>
       </c>
       <c r="E11" t="n">
-        <v>1.522470620717806e-06</v>
+        <v>1.522470620717809e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>9.464014253795316e-07</v>
+        <v>9.464014253795351e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>9.478522892591704e-07</v>
+        <v>9.478522892591724e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>9.43860279337881e-07</v>
+        <v>9.438602793378827e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>9.478772286293959e-07</v>
+        <v>9.478772286293972e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>9.458841255214962e-07</v>
+        <v>9.458841255214974e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>9.484059656511868e-07</v>
+        <v>9.484059656511882e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>9.480664365197214e-07</v>
+        <v>9.480664365197226e-07</v>
       </c>
       <c r="M11" t="n">
-        <v>9.474646048146964e-07</v>
+        <v>9.474646048146988e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>9.409502811672609e-07</v>
+        <v>9.409502811672626e-07</v>
       </c>
       <c r="O11" t="n">
-        <v>9.481327086625081e-07</v>
+        <v>9.4813270866251e-07</v>
       </c>
       <c r="P11" t="n">
-        <v>9.457951822755089e-07</v>
+        <v>9.4579518227551e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.451063561775572e-07</v>
+        <v>9.45106356177559e-07</v>
       </c>
       <c r="R11" t="n">
-        <v>9.453596960070386e-07</v>
+        <v>9.453596960070403e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>9.459314513692991e-07</v>
+        <v>9.459314513693016e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>9.470860822607553e-07</v>
+        <v>9.470860822607575e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>9.436908529961921e-07</v>
+        <v>9.436908529961938e-07</v>
       </c>
       <c r="V11" t="n">
         <v>1.180277988175574e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>9.256568567454665e-07</v>
+        <v>9.256568567454673e-07</v>
       </c>
       <c r="X11" t="n">
-        <v>9.46032571127216e-07</v>
+        <v>9.46032571127219e-07</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.466384079688766e-07</v>
+        <v>9.466384079688777e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.470780011950731e-07</v>
+        <v>9.470780011950749e-07</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.456719657696501e-07</v>
+        <v>9.456719657696519e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.480927568531379e-07</v>
+        <v>9.480927568531411e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>5.851032345249297e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.12317015357111e-06</v>
+        <v>5.85103234524935e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.85103234524935e-08</v>
@@ -6154,7 +6154,7 @@
         <v>9.791554511191092e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12317015357111e-06</v>
+        <v>7.363549235656493e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.029453026307028e-07</v>
@@ -6242,7 +6242,7 @@
         <v>7.705269981998474e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12317015357111e-06</v>
+        <v>7.705269981998474e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.705204383787008e-08</v>
@@ -6330,7 +6330,7 @@
         <v>1.350334423468467e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12317015357111e-06</v>
+        <v>1.083129520682058e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.156559747500319e-07</v>
@@ -6418,7 +6418,7 @@
         <v>3.263723979666428e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12317015357111e-06</v>
+        <v>3.263723979666428e-07</v>
       </c>
       <c r="O9" t="n">
         <v>3.464793278402158e-07</v>
@@ -6820,7 +6820,7 @@
         <v>9.497695022508826e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.51663274886358e-07</v>
+        <v>9.516632748863579e-07</v>
       </c>
       <c r="I2" t="n">
         <v>9.491102818461442e-07</v>
@@ -6847,7 +6847,7 @@
         <v>9.490562205175433e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.487630161859664e-07</v>
+        <v>9.487630161859665e-07</v>
       </c>
       <c r="R2" t="n">
         <v>9.491027170761443e-07</v>
@@ -6868,7 +6868,7 @@
         <v>9.579309800076425e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.508883008474007e-07</v>
+        <v>9.508883008474005e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>9.488888439388877e-07</v>
@@ -6890,85 +6890,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="E3" t="n">
         <v>1.548739928450562e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="J3" t="n">
         <v>9.626466215261914e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.201058378802613e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.626364896994764e-07</v>
+        <v>9.626364896994762e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7102,7 +7102,7 @@
         <v>5.367177705136292e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.579262924825274e-07</v>
+        <v>5.367177705136196e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.367177705136196e-08</v>
@@ -7190,7 +7190,7 @@
         <v>8.580571634056346e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.579262924825274e-07</v>
+        <v>6.496139955970497e-08</v>
       </c>
       <c r="O6" t="n">
         <v>9.00010940756233e-08</v>
@@ -7266,7 +7266,7 @@
         <v>6.877563772211318e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.924501530784316e-08</v>
+        <v>6.924501530784318e-08</v>
       </c>
       <c r="K7" t="n">
         <v>6.877563772211318e-08</v>
@@ -7278,7 +7278,7 @@
         <v>6.877563772211318e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.579262924825274e-07</v>
+        <v>6.877563772211318e-08</v>
       </c>
       <c r="O7" t="n">
         <v>6.877503891218739e-08</v>
@@ -7366,7 +7366,7 @@
         <v>1.146702787110332e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>6.579262924825274e-07</v>
+        <v>9.360500528599259e-08</v>
       </c>
       <c r="O8" t="n">
         <v>9.939392529222781e-08</v>
@@ -7454,7 +7454,7 @@
         <v>2.760413724771951e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>6.579262924825274e-07</v>
+        <v>2.760413724771951e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.926486378533724e-07</v>
@@ -7542,7 +7542,7 @@
         <v>9.559144368240346e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>9.481518469864694e-07</v>
+        <v>9.481518469864695e-07</v>
       </c>
       <c r="O10" t="n">
         <v>9.572312237325187e-07</v>
@@ -7575,7 +7575,7 @@
         <v>9.440269587950609e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.5571566180741e-07</v>
+        <v>9.557156618074098e-07</v>
       </c>
       <c r="Z10" t="n">
         <v>9.531481996879001e-07</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.468973528406318e-07</v>
+        <v>9.468973528406319e-07</v>
       </c>
       <c r="C11" t="n">
         <v>9.461851503274198e-07</v>
@@ -7609,7 +7609,7 @@
         <v>9.466706090028815e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>9.442093819679539e-07</v>
+        <v>9.44209381967954e-07</v>
       </c>
       <c r="H11" t="n">
         <v>9.41209579986484e-07</v>
@@ -7642,7 +7642,7 @@
         <v>9.459609031348008e-07</v>
       </c>
       <c r="R11" t="n">
-        <v>9.454169983372153e-07</v>
+        <v>9.454169983372154e-07</v>
       </c>
       <c r="S11" t="n">
         <v>9.430281246983028e-07</v>
@@ -7672,7 +7672,7 @@
         <v>9.404854281795983e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.471920399573964e-07</v>
+        <v>9.471920399573965e-07</v>
       </c>
     </row>
   </sheetData>
@@ -8050,7 +8050,7 @@
         <v>4.054739664223699e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>6.05647872815242e-07</v>
+        <v>6.056478728152421e-07</v>
       </c>
       <c r="O4" t="n">
         <v>2.328424210643886e-07</v>
@@ -8138,7 +8138,7 @@
         <v>5.250929650514895e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.056478728152421e-07</v>
+        <v>5.250929650514904e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.250929650514904e-08</v>
@@ -8226,7 +8226,7 @@
         <v>8.290041266231378e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.05647872815242e-07</v>
+        <v>6.335332685257975e-08</v>
       </c>
       <c r="O6" t="n">
         <v>6.353123516820032e-08</v>
@@ -8314,7 +8314,7 @@
         <v>6.684784238266602e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.05647872815242e-07</v>
+        <v>6.684784238266602e-08</v>
       </c>
       <c r="O7" t="n">
         <v>6.684723984270136e-08</v>
@@ -8402,7 +8402,7 @@
         <v>1.096530206694323e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>6.05647872815242e-07</v>
+        <v>9.007019349870049e-08</v>
       </c>
       <c r="O8" t="n">
         <v>9.545172440965501e-08</v>
@@ -8490,7 +8490,7 @@
         <v>2.524064983704564e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>6.05647872815242e-07</v>
+        <v>2.524064983704564e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.673237171080693e-07</v>
@@ -9174,7 +9174,7 @@
         <v>6.264730861876331e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.81896081160216e-06</v>
+        <v>6.264730861876357e-08</v>
       </c>
       <c r="O5" t="n">
         <v>6.264730861876357e-08</v>
@@ -9262,7 +9262,7 @@
         <v>7.898991315219415e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.81896081160216e-06</v>
+        <v>7.900221946218522e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.100767203135633e-07</v>
@@ -9350,7 +9350,7 @@
         <v>8.292652785023356e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.81896081160216e-06</v>
+        <v>8.292652785023356e-08</v>
       </c>
       <c r="O7" t="n">
         <v>8.292535722067103e-08</v>
@@ -9438,7 +9438,7 @@
         <v>1.449072161602878e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.81896081160216e-06</v>
+        <v>1.161074416741877e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.240218697031611e-07</v>
@@ -9526,7 +9526,7 @@
         <v>3.353059084306437e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81896081160216e-06</v>
+        <v>3.353059084306437e-07</v>
       </c>
       <c r="O9" t="n">
         <v>3.558410008306245e-07</v>
@@ -10210,7 +10210,7 @@
         <v>5.620997097176144e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00172175090613e-06</v>
+        <v>5.620997097176145e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.620997097176145e-08</v>
@@ -10298,7 +10298,7 @@
         <v>6.953018960979834e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00172175090613e-06</v>
+        <v>6.941372968370645e-08</v>
       </c>
       <c r="O6" t="n">
         <v>9.581826883586349e-08</v>
@@ -10386,7 +10386,7 @@
         <v>7.247814212680648e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00172175090613e-06</v>
+        <v>7.247814212680648e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.247740439815458e-08</v>
@@ -10474,7 +10474,7 @@
         <v>1.221678776559991e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00172175090613e-06</v>
+        <v>9.9262303538537e-08</v>
       </c>
       <c r="O8" t="n">
         <v>1.055569541460816e-07</v>
@@ -10562,7 +10562,7 @@
         <v>2.802540272117512e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.00172175090613e-06</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.97064151044139e-07</v>

--- a/Results/Phase 2/Hydrogen/hydrogen ozone depletion results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ozone depletion results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.619581029948397e-07</v>
+        <v>9.61958102994839e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.626325851845656e-07</v>
+        <v>9.626325851845651e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.69022336032707e-07</v>
+        <v>9.690223360327066e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.531537014725842e-06</v>
+        <v>1.531537014725845e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.675632076001189e-07</v>
+        <v>9.675632076001183e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.608785650047443e-07</v>
+        <v>9.608785650047439e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.676905314246021e-07</v>
+        <v>9.676905314246033e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.714195052735155e-07</v>
+        <v>9.714195052735153e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.637214261521951e-07</v>
+        <v>9.637214261521947e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.809679181080756e-07</v>
+        <v>9.809679181080749e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.636225834859507e-07</v>
+        <v>9.63622583485949e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.61787759843609e-07</v>
+        <v>9.617877598436086e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.793718667316782e-07</v>
+        <v>9.793718667316769e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.638864810890522e-07</v>
+        <v>9.638864810890513e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.639498622602155e-07</v>
+        <v>9.639498622602157e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.680268642517201e-07</v>
+        <v>9.680268642517191e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.660195433479876e-07</v>
+        <v>9.660195433479872e-07</v>
       </c>
       <c r="S2" t="n">
         <v>9.636058417370098e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.699320523239702e-07</v>
+        <v>9.699320523239692e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.636401170904861e-07</v>
+        <v>9.636401170904855e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.198906693270464e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.721205818912078e-07</v>
+        <v>9.721205818912072e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.632535754618583e-07</v>
+        <v>9.632535754618576e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>9.643203000785686e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.624089569038885e-07</v>
+        <v>9.624089569038881e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.630960961025373e-07</v>
+        <v>9.630960961025361e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.612037995203971e-07</v>
+        <v>9.612037995203962e-07</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55421396088876e-06</v>
+        <v>1.554213960888762e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.747890256761687e-07</v>
+        <v>9.747890256761685e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.214540573938143e-06</v>
+        <v>1.214540573938142e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.747557939218615e-07</v>
+        <v>9.747557939218603e-07</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.704729120865166e-07</v>
+        <v>6.704729120865132e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>9.375474773243492e-07</v>
+        <v>9.375474773243503e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.893247309007678e-06</v>
+        <v>2.893247309007683e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.768625804534024e-07</v>
+        <v>4.76862580453403e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.498981302006119e-06</v>
+        <v>2.498981302006118e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.856052357656948e-07</v>
+        <v>3.856052357656928e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.58325639340909e-06</v>
+        <v>2.583256393409086e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>3.661277461949749e-06</v>
+        <v>3.661277461949747e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.212261168178796e-06</v>
+        <v>1.212261168178795e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.479445195934864e-06</v>
+        <v>6.479445195934842e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.189405890309999e-06</v>
+        <v>1.18940589030998e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>7.010060369465709e-07</v>
+        <v>7.010060369465693e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>5.875798208281557e-06</v>
+        <v>5.875798208281561e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16453709203509e-06</v>
+        <v>1.164537092035092e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.224666103690352e-06</v>
+        <v>1.224666103690351e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.538252991875445e-06</v>
+        <v>2.53825299187544e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>2.024186627598535e-06</v>
+        <v>2.024186627598529e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.14372270851781e-06</v>
+        <v>1.143722708517812e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>3.181536418712438e-06</v>
+        <v>3.181536418712447e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.174679525844683e-06</v>
+        <v>1.174679525844688e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>9.281870901013725e-07</v>
+        <v>9.281870901013691e-07</v>
       </c>
       <c r="W4" t="n">
         <v>3.669728792873004e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.124398867308909e-06</v>
+        <v>1.124398867308912e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.401492146013274e-06</v>
+        <v>1.40149214601328e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.093771188718701e-07</v>
+        <v>8.093771188718697e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.051224196602469e-06</v>
+        <v>1.051224196602466e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.388642970910954e-07</v>
+        <v>5.388642970910935e-07</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.248947240726716e-07</v>
+        <v>1.248947240726718e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.464914061708121e-07</v>
+        <v>1.464914061708138e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.32091084227339e-07</v>
+        <v>1.320910842273385e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.806663810071761e-07</v>
+        <v>1.806663810071751e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.715648132204154e-07</v>
+        <v>1.715648132204138e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.710879207636232e-07</v>
+        <v>1.710879207636199e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>5.875798208281557e-06</v>
+        <v>1.352804653347076e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.451206649172879e-07</v>
+        <v>1.451206649172875e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.427085942356032e-07</v>
+        <v>1.427085942356038e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.15816706655715e-07</v>
+        <v>1.158167066557128e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635292e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.486720114520564e-07</v>
+        <v>1.486720114520557e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.617806295073627e-07</v>
+        <v>1.617806295073626e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.710969988953306e-07</v>
+        <v>1.710969988953294e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.200504048248096e-07</v>
+        <v>1.200504048248092e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.172397959823624e-07</v>
+        <v>2.172397959823607e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.240366617413052e-07</v>
+        <v>1.240366617413057e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.710879207635321e-07</v>
+        <v>1.710879207635291e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.193405771760805e-07</v>
+        <v>2.193405771760798e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.359111828164777e-07</v>
+        <v>3.35911182816478e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.962655702222264e-07</v>
+        <v>3.962655702222239e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>2.334949970499384e-07</v>
+        <v>2.334949970499372e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>4.143746089205649e-07</v>
+        <v>4.143746089205639e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>4.148514718378525e-07</v>
+        <v>4.148514718378506e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>5.875798208281557e-06</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>4.403772855923562e-07</v>
+        <v>4.403772855923545e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.460324216376804e-07</v>
+        <v>4.460324216376778e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.143746089205649e-07</v>
+        <v>4.143746089205639e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>5.080938899503726e-07</v>
+        <v>5.080938899503725e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.670681402198789e-07</v>
+        <v>3.670681402198774e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.143745793809691e-07</v>
+        <v>4.143745793809689e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.614610539882123e-07</v>
+        <v>9.614610539882118e-07</v>
       </c>
       <c r="C7" t="n">
         <v>9.576955147655761e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.202871274325203e-07</v>
+        <v>9.202871274325198e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.545753774738722e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.290581833776999e-07</v>
+        <v>9.290581833776993e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.678872430175534e-07</v>
+        <v>9.678872430175523e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.284030335574495e-07</v>
+        <v>9.284030335574478e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.06373908349608e-07</v>
+        <v>9.063739083496069e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.513912341778283e-07</v>
+        <v>9.513912341778277e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>8.50139057047274e-07</v>
+        <v>8.501390570472735e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.517044453549628e-07</v>
+        <v>9.517044453549626e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.627098340123095e-07</v>
+        <v>9.627098340123089e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>8.591774428762454e-07</v>
+        <v>8.591774428762443e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.499618113498911e-07</v>
+        <v>9.499618113498906e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.495619603547622e-07</v>
+        <v>9.49561960354761e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.259937269662677e-07</v>
+        <v>9.259937269662672e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.380214600120396e-07</v>
+        <v>9.38021460012039e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.517297320885053e-07</v>
+        <v>9.517297320885058e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.149964124981503e-07</v>
+        <v>9.149964124981495e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.51577657402054e-07</v>
+        <v>9.515776574020534e-07</v>
       </c>
       <c r="V7" t="n">
         <v>1.195829757432753e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>9.015879576134961e-07</v>
+        <v>9.015879576134955e-07</v>
       </c>
       <c r="X7" t="n">
         <v>9.540579120940051e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.476688642068522e-07</v>
+        <v>9.476688642068511e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.587965628828966e-07</v>
+        <v>9.587965628828964e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.548664406629229e-07</v>
+        <v>9.548664406629221e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.660864284680811e-07</v>
+        <v>9.660864284680806e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.559089539572069e-07</v>
+        <v>9.559089539572065e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.548701038005717e-07</v>
+        <v>9.548701038005709e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.442389191987162e-07</v>
+        <v>9.442389191987146e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.527687603066562e-06</v>
+        <v>1.52768760306656e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.467706491728809e-07</v>
+        <v>9.467706491728796e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.577533524545106e-07</v>
+        <v>9.5775335245451e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.465998777413121e-07</v>
+        <v>9.46599877741312e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.403055294180005e-07</v>
+        <v>9.403055294180008e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.530753564561126e-07</v>
+        <v>9.530753564561114e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.242669057001614e-07</v>
+        <v>9.242669057001605e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.531341464277221e-07</v>
+        <v>9.531341464277225e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.563068096965661e-07</v>
+        <v>9.563068096965655e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.26783348679572e-07</v>
+        <v>9.267833486795716e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.526051400050713e-07</v>
+        <v>9.526051400050699e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.524865876992014e-07</v>
+        <v>9.524865876992016e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.458399683914375e-07</v>
+        <v>9.458399683914374e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.493053043536426e-07</v>
+        <v>9.493053043536414e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.531289102231286e-07</v>
+        <v>9.53128910223128e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.427413433343326e-07</v>
+        <v>9.427413433343321e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.53093991109635e-07</v>
+        <v>9.53093991109633e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.190393212132678e-06</v>
+        <v>1.190393212132679e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.388289831988421e-07</v>
+        <v>9.388289831988416e-07</v>
       </c>
       <c r="X8" t="n">
         <v>9.538359732699484e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.519956607373162e-07</v>
+        <v>9.519956607373148e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.551474559221074e-07</v>
+        <v>9.55147455922106e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.540463769861119e-07</v>
+        <v>9.540463769861111e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.57259210611299e-07</v>
+        <v>9.572592106112981e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.488014523265724e-07</v>
+        <v>9.488014523265731e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.501931035083015e-07</v>
+        <v>9.501931035083011e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.501718843995522e-07</v>
+        <v>9.501718843995526e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.52546483921036e-06</v>
+        <v>1.525464839210358e-06</v>
       </c>
       <c r="F2" t="n">
         <v>9.490019370267313e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.500991019345264e-07</v>
+        <v>9.500991019345267e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.517146651445299e-07</v>
+        <v>9.517146651445296e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.494561622391296e-07</v>
+        <v>9.494561622391295e-07</v>
       </c>
       <c r="J2" t="n">
         <v>9.505490904159939e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.502977867321041e-07</v>
+        <v>9.502977867321035e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.497289901121628e-07</v>
+        <v>9.497289901121617e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.496300021775033e-07</v>
+        <v>9.49630002177504e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.511020056791232e-07</v>
+        <v>9.511020056791231e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.49046888877427e-07</v>
+        <v>9.490468888774274e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.504378225805859e-07</v>
+        <v>9.504378225805854e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.494111725356344e-07</v>
+        <v>9.494111725356347e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.495705957435656e-07</v>
+        <v>9.495705957435643e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.503988827248064e-07</v>
+        <v>9.503988827248062e-07</v>
       </c>
       <c r="T2" t="n">
         <v>9.49556108487673e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.503716965549107e-07</v>
+        <v>9.503716965549103e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.186175853561128e-06</v>
+        <v>1.186175853561129e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.591769641203576e-07</v>
+        <v>9.591769641203574e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.514512416411304e-07</v>
+        <v>9.514512416411307e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.499925198326977e-07</v>
+        <v>9.499925198326969e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.506382296553024e-07</v>
+        <v>9.506382296553033e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.531419648581428e-07</v>
+        <v>9.53141964858143e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.488528193980075e-07</v>
+        <v>9.488528193980072e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.548880099135345e-06</v>
+        <v>1.548880099135344e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.634010553554001e-07</v>
+        <v>9.634010553554009e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.202065712731062e-06</v>
+        <v>1.202065712731063e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.63356147217283e-07</v>
+        <v>9.633561472172835e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.460534390265269e-07</v>
+        <v>1.460534390265263e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.951146113805316e-07</v>
+        <v>4.951146113805313e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.962332620948367e-07</v>
+        <v>4.962332620948371e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.228180429862068e-07</v>
+        <v>2.228180429862063e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.070933968444944e-07</v>
+        <v>2.070933968444938e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.378716103953761e-07</v>
+        <v>4.378716103953747e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.422129322735165e-07</v>
+        <v>9.422129322735164e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.258906025725874e-07</v>
+        <v>3.258906025725881e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.567121791575843e-07</v>
+        <v>5.567121791575842e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.996116783971337e-07</v>
+        <v>4.996116783971329e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>3.64100970166927e-07</v>
+        <v>3.641009701669265e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.67706289157306e-07</v>
+        <v>3.677062891573055e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>7.467289608181308e-07</v>
+        <v>7.467289608181307e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.017714483622736e-07</v>
+        <v>2.017714483622733e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.148506361989629e-07</v>
+        <v>5.148506361989622e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.977451221221646e-07</v>
+        <v>2.977451221221643e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>3.62144247187891e-07</v>
+        <v>3.621442471878902e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.069372071933419e-07</v>
+        <v>5.06937207193341e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.525102180945309e-07</v>
+        <v>3.525102180945304e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>5.021103927677807e-07</v>
+        <v>5.021103927677788e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.908463292269204e-07</v>
+        <v>6.908463292269205e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.759689770526062e-06</v>
+        <v>2.75968977052606e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>7.995845221078491e-07</v>
+        <v>7.995845221078499e-07</v>
       </c>
       <c r="Y4" t="n">
         <v>4.553680336804668e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.414078527295813e-07</v>
+        <v>5.41407852729582e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.257714712442687e-06</v>
+        <v>1.257714712442688e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.739437801250163e-07</v>
+        <v>1.739437801250157e-07</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.877889743789499e-08</v>
+        <v>8.877889743789467e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="E5" t="n">
         <v>1.017144969076725e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.308924623362656e-08</v>
+        <v>9.308924623362644e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.221840201706177e-07</v>
+        <v>1.221840201706171e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.169230006116954e-07</v>
+        <v>1.169230006116952e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.164468831077563e-07</v>
+        <v>1.164468831077557e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>7.467289608181308e-07</v>
+        <v>9.499956544077903e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.00893474521041e-07</v>
+        <v>1.008934745210404e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>9.944873499257837e-08</v>
+        <v>9.944873499257777e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.334150678230065e-08</v>
+        <v>8.334150678230024e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.024518355483182e-07</v>
+        <v>1.024518355483174e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.115097137827382e-07</v>
+        <v>1.115097137827378e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16452320584925e-07</v>
+        <v>1.164523205849241e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>8.587733260032625e-08</v>
+        <v>8.587733260032595e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.431171327492489e-07</v>
+        <v>1.431171327492483e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.826495040522483e-08</v>
+        <v>8.826495040522446e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.164468831075853e-07</v>
+        <v>1.164468831075843e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.453484076306165e-07</v>
+        <v>1.453484076306155e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.117831689198837e-07</v>
+        <v>2.117831689198834e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.472127433440841e-07</v>
+        <v>2.472127433440836e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.516622393267401e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.578432138349902e-07</v>
+        <v>2.578432138349895e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.583193155044905e-07</v>
+        <v>2.583193155044898e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.467289608181308e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.731074524093661e-07</v>
+        <v>2.731074524093653e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.764271624090685e-07</v>
+        <v>2.764271624090681e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.578432138349902e-07</v>
+        <v>2.578432138349895e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="V6" t="n">
         <v>3.141616073501754e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.300731025701802e-07</v>
+        <v>2.3007310257018e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.578431980003794e-07</v>
+        <v>2.578431980003789e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.611113635927624e-07</v>
+        <v>9.611113635927619e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.52982461630492e-07</v>
+        <v>9.529824616304922e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.531187831143741e-07</v>
+        <v>9.53118783114374e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5448239965017e-06</v>
+        <v>1.544823996501698e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.599883629584193e-07</v>
+        <v>9.599883629584199e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.533969682164676e-07</v>
+        <v>9.533969682164684e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.442119605225936e-07</v>
+        <v>9.44211960522594e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.573224869670249e-07</v>
+        <v>9.573224869670253e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.511112124600484e-07</v>
+        <v>9.511112124600488e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.52365730002137e-07</v>
+        <v>9.523657300021383e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.556420737854217e-07</v>
+        <v>9.556420737854219e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.563197265234012e-07</v>
+        <v>9.56319726523402e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.476041562281051e-07</v>
+        <v>9.476041562281057e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.596471706415462e-07</v>
+        <v>9.596471706415471e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.513525901025644e-07</v>
+        <v>9.513525901025643e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.575598616022946e-07</v>
+        <v>9.575598616022941e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.566673593856007e-07</v>
+        <v>9.566673593856001e-07</v>
       </c>
       <c r="S7" t="n">
         <v>9.516442830650868e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.567299278466835e-07</v>
+        <v>9.567299278466841e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.518309902575324e-07</v>
+        <v>9.518309902575333e-07</v>
       </c>
       <c r="V7" t="n">
         <v>1.185574782378262e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.998932573223985e-07</v>
+        <v>8.998932573223984e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.45607834814498e-07</v>
+        <v>9.45607834814499e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.541145864208871e-07</v>
+        <v>9.541145864208876e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.501986624353056e-07</v>
+        <v>9.501986624353058e-07</v>
       </c>
       <c r="AA7" t="n">
         <v>9.355343136948829e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.608458180945585e-07</v>
+        <v>9.608458180945589e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.477800686237142e-07</v>
+        <v>9.477800686237144e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.45473043507337e-07</v>
+        <v>9.454730435073368e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.455138511081851e-07</v>
+        <v>9.45513851108185e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.52361929958602e-06</v>
+        <v>1.523619299586019e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.474695844564569e-07</v>
+        <v>9.474695844564566e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.455676437511349e-07</v>
+        <v>9.455676437511352e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.430039991895441e-07</v>
+        <v>9.43003999189543e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.46710827597128e-07</v>
+        <v>9.467108275971283e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.449571727332037e-07</v>
+        <v>9.449571727332048e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.452971118748314e-07</v>
+        <v>9.452971118748309e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.462190621173723e-07</v>
+        <v>9.462190621173714e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.464284083380456e-07</v>
+        <v>9.46428408338046e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.439347995804305e-07</v>
+        <v>9.439347995804308e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.473592927156605e-07</v>
+        <v>9.473592927156613e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.449761658403212e-07</v>
+        <v>9.449761658403227e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.467738441091482e-07</v>
+        <v>9.467738441091491e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.465271759642482e-07</v>
+        <v>9.465271759642472e-07</v>
       </c>
       <c r="S8" t="n">
         <v>9.450699472120605e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.465411575575429e-07</v>
+        <v>9.465411575575427e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.451277134097278e-07</v>
+        <v>9.451277134097287e-07</v>
       </c>
       <c r="V8" t="n">
         <v>1.178672427697127e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.303011469739549e-07</v>
+        <v>9.303011469739553e-07</v>
       </c>
       <c r="X8" t="n">
         <v>9.433757029373479e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.457875802192306e-07</v>
+        <v>9.457875802192301e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.446515321490872e-07</v>
+        <v>9.446515321490866e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.404829419425281e-07</v>
+        <v>9.404829419425276e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.477106116472236e-07</v>
+        <v>9.477106116472243e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2130,64 +2130,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.582052722574824e-07</v>
+        <v>9.582052722574818e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.593548868957311e-07</v>
+        <v>9.593548868957307e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.602793076266584e-07</v>
+        <v>9.60279307626658e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.530975294498375e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.613412672196641e-07</v>
+        <v>9.613412672196637e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.578662359884099e-07</v>
+        <v>9.578662359884095e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.623276883666127e-07</v>
+        <v>9.623276883666121e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.639166265208075e-07</v>
+        <v>9.639166265208077e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.600789723825422e-07</v>
+        <v>9.600789723825424e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.742177375606117e-07</v>
+        <v>9.742177375606111e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.583821660579382e-07</v>
+        <v>9.583821660579374e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.583779478639268e-07</v>
+        <v>9.58377947863927e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.69392356455114e-07</v>
+        <v>9.693923564551138e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.595188052682945e-07</v>
+        <v>9.595188052682941e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.598556689119788e-07</v>
+        <v>9.598556689119784e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.626231155413347e-07</v>
+        <v>9.626231155413345e-07</v>
       </c>
       <c r="R2" t="n">
         <v>9.617146713055765e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.598474377237906e-07</v>
+        <v>9.598474377237902e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.607777545503467e-07</v>
+        <v>9.607777545503463e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.590954082857486e-07</v>
+        <v>9.590954082857482e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.195071959365129e-06</v>
@@ -2199,16 +2199,16 @@
         <v>9.606713058849135e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.620153914483069e-07</v>
+        <v>9.620153914483065e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>9.592872481140813e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.59592398844426e-07</v>
+        <v>9.595923988444258e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.583703220981986e-07</v>
+        <v>9.583703220981979e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55303592774959e-06</v>
+        <v>1.553035927749591e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.72087337098149e-07</v>
+        <v>9.720873370981496e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.211430162738689e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.720461101555899e-07</v>
+        <v>9.720461101555902e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.576846954420364e-07</v>
+        <v>3.576846954419963e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.986721093746858e-07</v>
+        <v>6.986721093746847e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>9.829315329216313e-07</v>
+        <v>9.829315329216277e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.118986072098367e-07</v>
+        <v>6.1189860720984e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.284517535207156e-06</v>
+        <v>1.284517535207157e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.761073458999567e-07</v>
+        <v>2.761073458999635e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.619339857696771e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.039818077529423e-06</v>
+        <v>2.039818077529425e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.70564395678652e-07</v>
+        <v>8.705643956786342e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.573006167663608e-06</v>
+        <v>4.573006167663612e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.229682153965718e-07</v>
+        <v>4.229682153964957e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.46821385661573e-07</v>
+        <v>4.468213856615667e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.478799437613892e-06</v>
+        <v>3.478799437613896e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>6.723281285200666e-07</v>
+        <v>6.723281285200678e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>7.826837442168413e-07</v>
+        <v>7.826837442168636e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.609020589099758e-06</v>
+        <v>1.609020589099755e-06</v>
       </c>
       <c r="R4" t="n">
         <v>1.422618762266418e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>7.855494322273132e-07</v>
+        <v>7.855494322273114e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.123488610097119e-06</v>
+        <v>1.123488610097126e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>6.062534025972346e-07</v>
+        <v>6.062534025972351e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.598636493685245e-07</v>
+        <v>6.598636493685228e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.65920678559657e-06</v>
+        <v>4.659206785596574e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.076506577669528e-06</v>
+        <v>1.076506577669549e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.40099618460282e-06</v>
+        <v>1.400996184602817e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.407586551837898e-07</v>
+        <v>6.407586551837873e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.55158536064008e-07</v>
+        <v>7.551585360640106e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.603037022775219e-07</v>
+        <v>4.603037022775276e-07</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.117595350705767e-07</v>
+        <v>1.117595350705758e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.300005806570915e-07</v>
+        <v>1.300005806570917e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.178377434290374e-07</v>
+        <v>1.178377434290367e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.588655364447827e-07</v>
+        <v>1.58865536444782e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.512546771699643e-07</v>
+        <v>1.512546771699631e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.507753525386233e-07</v>
+        <v>1.507753525386227e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.478799437613892e-06</v>
+        <v>1.205315667628564e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28842821629409e-07</v>
+        <v>1.288428216294087e-07</v>
       </c>
       <c r="P5" t="n">
         <v>1.268055322405809e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.040920364798264e-07</v>
+        <v>1.040920364798263e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384621e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.319231947650228e-07</v>
+        <v>1.319231947650224e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.435112130847452e-07</v>
+        <v>1.43511213084744e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5078302013474e-07</v>
+        <v>1.507830201347396e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.076679135967682e-07</v>
+        <v>1.076679135967668e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.898945380859946e-07</v>
+        <v>1.898945380859936e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.110347962409687e-07</v>
+        <v>1.110347962409688e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.507753525384622e-07</v>
+        <v>1.507753525384619e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.915306362135415e-07</v>
+        <v>1.915306362135406e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.767612534944521e-07</v>
+        <v>2.767612534944507e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.249240717185364e-07</v>
+        <v>3.249240717185356e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.950331082791471e-07</v>
+        <v>1.950331082791464e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>3.393750897228697e-07</v>
+        <v>3.393750897228694e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>3.398543920790535e-07</v>
+        <v>3.39854392079052e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.478799437613892e-06</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.601252330631336e-07</v>
+        <v>3.601252330631338e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.646380332271436e-07</v>
+        <v>3.646380332271433e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.393750897228697e-07</v>
+        <v>3.393750897228694e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>4.148189544076857e-07</v>
+        <v>4.148189544076844e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.016245143166903e-07</v>
+        <v>3.016245143166904e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.393750674475517e-07</v>
+        <v>3.393750674475509e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2570,82 +2570,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.651096148148533e-07</v>
+        <v>9.651096148148546e-07</v>
       </c>
       <c r="C7" t="n">
         <v>9.584670426252898e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.530679645979239e-07</v>
+        <v>9.530679645979236e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.540945428642295e-06</v>
+        <v>1.540945428642294e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.469705383114753e-07</v>
+        <v>9.469705383114745e-07</v>
       </c>
       <c r="G7" t="n">
         <v>9.671293443167193e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.412785064250502e-07</v>
+        <v>9.412785064250506e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.318376901062039e-07</v>
+        <v>9.318376901062036e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.543979927401785e-07</v>
+        <v>9.543979927401783e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>8.712804939948408e-07</v>
+        <v>8.71280493994841e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.641074695013146e-07</v>
+        <v>9.641074695013159e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.642350505474377e-07</v>
+        <v>9.642350505474379e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>8.993818080810612e-07</v>
+        <v>8.99381808081061e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.572791001538543e-07</v>
+        <v>9.572791001538546e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.552579447135898e-07</v>
+        <v>9.5525794471359e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.392553659379537e-07</v>
+        <v>9.392553659379541e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.447682427361413e-07</v>
+        <v>9.44768242736141e-07</v>
       </c>
       <c r="S7" t="n">
         <v>9.553917121043125e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.501622090580493e-07</v>
+        <v>9.501622090580495e-07</v>
       </c>
       <c r="U7" t="n">
         <v>9.598787469299355e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.197213161843001e-06</v>
+        <v>1.197213161843e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.723278431444999e-07</v>
+        <v>8.723278431444996e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.507513380449664e-07</v>
+        <v>9.507513380449673e-07</v>
       </c>
       <c r="Y7" t="n">
         <v>9.427249822727383e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.586875841951112e-07</v>
+        <v>9.586875841951118e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.569902351755463e-07</v>
+        <v>9.569902351755467e-07</v>
       </c>
       <c r="AB7" t="n">
         <v>9.64251684974553e-07</v>
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.550491447721482e-07</v>
+        <v>9.550491447721478e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.531763678955241e-07</v>
+        <v>9.531763678955237e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.516441909181593e-07</v>
+        <v>9.516441909181585e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.525474078874421e-06</v>
+        <v>1.52547407887442e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.499318021194858e-07</v>
+        <v>9.49931802119486e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.556290918629207e-07</v>
+        <v>9.556290918629205e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.483283306186818e-07</v>
+        <v>9.483283306186814e-07</v>
       </c>
       <c r="I8" t="n">
         <v>9.45621667261705e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.520302643270694e-07</v>
+        <v>9.520302643270696e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.28369061086505e-07</v>
+        <v>9.283690610865054e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.547700592612958e-07</v>
+        <v>9.54770059261296e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.548238908498478e-07</v>
+        <v>9.548238908498474e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.363298674438123e-07</v>
+        <v>9.363298674438127e-07</v>
       </c>
       <c r="O8" t="n">
         <v>9.527997686578361e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.522170001351597e-07</v>
+        <v>9.522170001351599e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.477032224244088e-07</v>
+        <v>9.47703222424409e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.493031547003224e-07</v>
+        <v>9.49303154700322e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.522696335360418e-07</v>
+        <v>9.522696335360421e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.508205098111111e-07</v>
+        <v>9.508205098111114e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.535592192429897e-07</v>
+        <v>9.535592192429892e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.188603178650697e-06</v>
+        <v>1.188603178650696e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.285629481865744e-07</v>
+        <v>9.285629481865741e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.509821167121677e-07</v>
+        <v>9.509821167121676e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.486741848207186e-07</v>
+        <v>9.486741848207188e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.532090762309668e-07</v>
+        <v>9.532090762309672e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.527419277482799e-07</v>
+        <v>9.527419277482802e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.548238338014667e-07</v>
+        <v>9.548238338014663e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.531795218576767e-07</v>
+        <v>9.531795218576778e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.580192756650442e-07</v>
+        <v>9.580192756650444e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.564574876411831e-07</v>
+        <v>9.564574876411852e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.531157452608472e-06</v>
+        <v>1.531157452608474e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.541312690000764e-07</v>
+        <v>9.541312690000776e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.534298307058813e-07</v>
+        <v>9.534298307058821e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.564065465958478e-07</v>
+        <v>9.564065465958486e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.545350301783789e-07</v>
+        <v>9.545350301783796e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.550412667072907e-07</v>
+        <v>9.550412667072921e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.536627759873892e-07</v>
+        <v>9.536627759873905e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.529444541826125e-07</v>
+        <v>9.529444541826129e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.539180913647237e-07</v>
+        <v>9.539180913647241e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.595922589912824e-07</v>
+        <v>9.59592258991283e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.538515110224299e-07</v>
+        <v>9.538515110224306e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.549478486447063e-07</v>
+        <v>9.549478486447069e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.555575110527999e-07</v>
+        <v>9.555575110528006e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.554578044936267e-07</v>
+        <v>9.554578044936275e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.548982969589901e-07</v>
+        <v>9.548982969589909e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.540695825292549e-07</v>
+        <v>9.540695825292555e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.550301437794642e-07</v>
+        <v>9.550301437794657e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.189811989769135e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.68121904600934e-07</v>
+        <v>9.681219046009351e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.554533720341323e-07</v>
+        <v>9.554533720341334e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.551715727920272e-07</v>
+        <v>9.551715727920279e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.546606530849469e-07</v>
+        <v>9.546606530849475e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.545220325912559e-07</v>
+        <v>9.545220325912565e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.537043917267767e-07</v>
+        <v>9.537043917267772e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="E3" t="n">
         <v>1.551865896961909e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.676031866292419e-07</v>
+        <v>9.676031866292425e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.206289476249775e-06</v>
+        <v>1.206289476249774e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.675631894626869e-07</v>
+        <v>9.675631894626873e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.97675426836221e-07</v>
+        <v>1.976754268362244e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397472425441015e-06</v>
+        <v>1.397472425441017e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.072138591869942e-06</v>
+        <v>1.072138591869943e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.159238025284089e-07</v>
+        <v>9.159238025284078e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6109320834057e-07</v>
+        <v>4.61093208340571e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.582649637088305e-07</v>
+        <v>2.582649637088019e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.110489054387515e-06</v>
+        <v>1.110489054387519e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.752572787560618e-07</v>
+        <v>5.752572787560613e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.59006921131162e-07</v>
+        <v>6.590069211311531e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.241666448052443e-07</v>
+        <v>3.241666448052422e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.446048761855098e-07</v>
+        <v>1.446048761855069e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.123144077048307e-07</v>
+        <v>4.123144077048274e-07</v>
       </c>
       <c r="N4" t="n">
         <v>1.864463093171687e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>3.473651252283995e-07</v>
+        <v>3.473651252284008e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>6.130317828566886e-07</v>
+        <v>6.130317828566744e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.073006724415956e-07</v>
+        <v>8.073006724415972e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.337885574451113e-07</v>
+        <v>8.337885574451134e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>6.06623109861176e-07</v>
+        <v>6.066231098611753e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>4.483967345026842e-07</v>
+        <v>4.483967345026843e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.520945191815716e-07</v>
+        <v>6.520945191815743e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>5.70007471676329e-07</v>
+        <v>5.700074716763327e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.995987498261675e-06</v>
+        <v>3.995987498261672e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>7.984906456636283e-07</v>
+        <v>7.984906456636309e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.064484100591112e-07</v>
+        <v>7.064484100591195e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.280791573072921e-07</v>
+        <v>5.280791573072936e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.462523766728874e-07</v>
+        <v>5.462523766728853e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.680690971429594e-07</v>
+        <v>3.680690971429616e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.634915099442151e-08</v>
+        <v>9.634915099442298e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.110641376785499e-07</v>
+        <v>1.110641376785514e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.012524200894141e-07</v>
+        <v>1.012524200894145e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.343493949911203e-07</v>
+        <v>1.343493949911229e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.282998975734243e-07</v>
+        <v>1.282998975734251e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27823072368232e-07</v>
+        <v>1.278230723682335e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.278230723684692e-07</v>
+        <v>1.278230723684701e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.864463093171686e-06</v>
+        <v>1.034255178058068e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.101301775897279e-07</v>
+        <v>1.101301775897308e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.084867034745363e-07</v>
+        <v>1.084867034745376e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.016380711293337e-08</v>
+        <v>9.01638071129371e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.122703511519082e-07</v>
+        <v>1.122703511519101e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.221825154144337e-07</v>
+        <v>1.221825154144357e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.278292577983471e-07</v>
+        <v>1.278292577983486e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>9.30484544868775e-08</v>
+        <v>9.304845448687771e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.587906091757308e-07</v>
+        <v>1.587906091757356e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.576450675424374e-08</v>
+        <v>9.576450675424604e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.278230723682319e-07</v>
+        <v>1.278230723682333e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.60700214959909e-07</v>
+        <v>1.607002149599106e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.311305662754694e-07</v>
+        <v>2.311305662754664e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.703396833691387e-07</v>
+        <v>2.703396833691497e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.645960790142378e-07</v>
+        <v>1.645960790142467e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.821041871491802e-07</v>
+        <v>2.821041871491724e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.825809966918923e-07</v>
+        <v>2.825809966918921e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.821041714867013e-07</v>
+        <v>2.82104171486703e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.864463093171687e-06</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.989967783624569e-07</v>
+        <v>2.98996778362471e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.02670627123293e-07</v>
+        <v>3.026706271233097e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.821041871491802e-07</v>
+        <v>2.821041871491724e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.440987298683509e-07</v>
+        <v>3.440987298683446e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.821041714867013e-07</v>
+        <v>2.82104171486703e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.513716265135523e-07</v>
+        <v>2.51371626513559e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.821041714867015e-07</v>
+        <v>2.821041714867033e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.640622453070803e-07</v>
+        <v>9.640622453070818e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.357304804225079e-07</v>
+        <v>9.357304804225098e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.449155917822114e-07</v>
+        <v>9.449155917822128e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.531684343761015e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.585855806739462e-07</v>
+        <v>9.585855806739469e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.625758969065524e-07</v>
+        <v>9.625758969065545e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.453647881173047e-07</v>
+        <v>9.453647881173046e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.561977868781858e-07</v>
+        <v>9.561977868781852e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.533833028259496e-07</v>
+        <v>9.533833028259508e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.612767853975257e-07</v>
+        <v>9.612767853975265e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.654739813189804e-07</v>
+        <v>9.654739813189812e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.598197339233129e-07</v>
+        <v>9.598197339233142e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.263800153365447e-07</v>
+        <v>9.263800153365461e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.600562846923986e-07</v>
+        <v>9.600562846923992e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.53514399558906e-07</v>
+        <v>9.535143995589076e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.501427681422216e-07</v>
+        <v>9.501427681422225e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.508374850235581e-07</v>
+        <v>9.50837485023559e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.538793744029967e-07</v>
+        <v>9.538793744029978e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.589083286334927e-07</v>
+        <v>9.589083286334934e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.531293116656376e-07</v>
+        <v>9.531293116656384e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.193047443933629e-06</v>
+        <v>1.193047443933628e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.75900554285051e-07</v>
+        <v>8.759005542850517e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.507810852584624e-07</v>
+        <v>9.507810852584619e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.523577057159919e-07</v>
+        <v>9.523577057159934e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.552643933800187e-07</v>
+        <v>9.552643933800189e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.561759349870801e-07</v>
+        <v>9.561759349870807e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.61043424337816e-07</v>
+        <v>9.610434243378166e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.51586581110029e-07</v>
+        <v>9.515865811100303e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.435352916069382e-07</v>
+        <v>9.43535291606939e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.461527585229565e-07</v>
+        <v>9.461527585229578e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.521974781587271e-06</v>
+        <v>1.521974781587274e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.500464283912585e-07</v>
+        <v>9.500464283912591e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.511605966992815e-07</v>
+        <v>9.511605966992828e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.463062032415916e-07</v>
+        <v>9.463062032415915e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.493637357830408e-07</v>
+        <v>9.493637357830421e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.485711742607117e-07</v>
+        <v>9.485711742607132e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.508024421041607e-07</v>
+        <v>9.508024421041613e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.519938578193149e-07</v>
+        <v>9.519938578193157e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.503947944173801e-07</v>
+        <v>9.503947944173808e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.408537835208981e-07</v>
+        <v>9.408537835208999e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.504358454288617e-07</v>
+        <v>9.504358454288629e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.485556044676503e-07</v>
+        <v>9.485556044676501e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.476311638363987e-07</v>
+        <v>9.476311638363999e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.478475556721654e-07</v>
+        <v>9.47847555672167e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.486721174991001e-07</v>
+        <v>9.486721174991006e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.50131593270566e-07</v>
+        <v>9.501315932705674e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.484626833837686e-07</v>
+        <v>9.484626833837691e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.183786822865436e-06</v>
+        <v>1.183786822865435e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.264151134836235e-07</v>
+        <v>9.264151134836246e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.478174611398158e-07</v>
+        <v>9.478174611398178e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.482530292302787e-07</v>
+        <v>9.482530292302798e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.490646616733951e-07</v>
+        <v>9.490646616733956e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.493407955158282e-07</v>
+        <v>9.493407955158292e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.50737877817701e-07</v>
+        <v>9.507378778177022e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.504461641586008e-07</v>
+        <v>9.504461641586005e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.55630585862916e-07</v>
+        <v>9.556305858629175e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.50949402985478e-07</v>
+        <v>9.509494029854789e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.528139211321622e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.516320842614999e-07</v>
+        <v>9.516320842615016e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.507197419572617e-07</v>
+        <v>9.507197419572623e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.531807244520324e-07</v>
+        <v>9.531807244520328e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.507336228929854e-07</v>
+        <v>9.507336228929855e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.519773132698765e-07</v>
+        <v>9.519773132698761e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.504111673483457e-07</v>
+        <v>9.504111673483461e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.506027504257539e-07</v>
+        <v>9.506027504257537e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.509862619250302e-07</v>
+        <v>9.509862619250299e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.548550468634249e-07</v>
+        <v>9.548550468634257e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.505529727792816e-07</v>
+        <v>9.505529727792839e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.519168943088786e-07</v>
+        <v>9.519168943088801e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.523832370768246e-07</v>
+        <v>9.523832370768253e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.522586565932665e-07</v>
+        <v>9.52258656593268e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.518549053616758e-07</v>
+        <v>9.51854905361678e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.512070811403898e-07</v>
+        <v>9.51207081140391e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.531863903548158e-07</v>
+        <v>9.531863903548171e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.187015319351125e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.639014264440048e-07</v>
+        <v>9.639014264440057e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.518348187128585e-07</v>
+        <v>9.518348187128599e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.514571816077873e-07</v>
+        <v>9.514571816077872e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.511750955750177e-07</v>
+        <v>9.511750955750182e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.520290368923646e-07</v>
+        <v>9.520290368923662e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.506013115249709e-07</v>
+        <v>9.506013115249718e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.550155368777399e-06</v>
+        <v>1.5501553687774e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.646608263943951e-07</v>
+        <v>9.646608263943962e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.203208816387312e-06</v>
+        <v>1.203208816387313e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.646138578383352e-07</v>
+        <v>9.646138578383361e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.395551426867456e-07</v>
+        <v>2.395551426867447e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.516453659292818e-06</v>
+        <v>1.516453659292819e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>3.850550247946197e-07</v>
+        <v>3.850550247946198e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.577592810431845e-07</v>
+        <v>5.577592810431846e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.668657947153557e-07</v>
+        <v>5.668657947153551e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.037908494301616e-07</v>
+        <v>3.037908494301608e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.029739624725611e-06</v>
+        <v>1.029739624725613e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>3.380399697208386e-07</v>
+        <v>3.380399697208377e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.166890099901325e-07</v>
+        <v>6.166890099901332e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.460063515938048e-07</v>
+        <v>2.46006351593806e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.86246517270868e-07</v>
+        <v>2.862465172708705e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.006526722443991e-07</v>
+        <v>4.006526722443981e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.399695324057145e-06</v>
+        <v>1.399695324057147e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>2.62318485103631e-07</v>
+        <v>2.623184851036316e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.720748407511292e-07</v>
+        <v>5.72074840751128e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.271046145594575e-07</v>
+        <v>7.271046145594579e-07</v>
       </c>
       <c r="R4" t="n">
         <v>7.587820779859649e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.712077251297895e-07</v>
+        <v>5.712077251297907e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>4.646587979068962e-07</v>
+        <v>4.64658797906896e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>8.857923428824048e-07</v>
+        <v>8.857923428824051e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.208873975270637e-07</v>
+        <v>6.208873975270732e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.673072986763805e-06</v>
+        <v>3.673072986763807e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>6.030395788213388e-07</v>
+        <v>6.030395788213396e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.139676838241179e-07</v>
+        <v>5.139676838241157e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.86883696937948e-07</v>
+        <v>3.868836969379478e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.579283416690995e-07</v>
+        <v>6.579283416690994e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.15125787721825e-07</v>
+        <v>3.15125787721824e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.081017963165004e-08</v>
+        <v>9.081017963164849e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.044615545942339e-07</v>
+        <v>1.044615545942353e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.53590362777993e-08</v>
+        <v>9.535903627780004e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.260637337575427e-07</v>
+        <v>1.260637337575435e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.204857621216382e-07</v>
+        <v>1.204857621216405e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.200091392695256e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.200091392697698e-07</v>
+        <v>1.200091392697696e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.399695324057145e-06</v>
+        <v>9.737506064886252e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.035951019391928e-07</v>
+        <v>1.035951019391942e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.020704195259704e-07</v>
+        <v>1.020704195259708e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.507191765083889e-08</v>
+        <v>8.50719176508407e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.051075353542653e-07</v>
+        <v>1.051075353542663e-07</v>
       </c>
       <c r="V5" t="n">
         <v>1.144823545756015e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.200148776184447e-07</v>
+        <v>1.200148776184463e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>8.774806026985643e-08</v>
+        <v>8.774806026985756e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.479290711720992e-07</v>
+        <v>1.479290711720987e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.026779397237197e-08</v>
+        <v>9.026779397237144e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.200091392695258e-07</v>
+        <v>1.200091392695262e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.50509894112088e-07</v>
+        <v>1.505098941120862e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.107494842494841e-07</v>
+        <v>2.107494842494846e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.460396248338793e-07</v>
+        <v>2.460396248338799e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.508651618468604e-07</v>
+        <v>1.508651618468603e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.566282588832383e-07</v>
+        <v>2.566282588832366e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.571048694935339e-07</v>
+        <v>2.571048694935338e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5662824664142e-07</v>
+        <v>2.56628246641419e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.399695324057145e-06</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.718324247237247e-07</v>
+        <v>2.718324247237255e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.751390699344819e-07</v>
+        <v>2.751390699344816e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.566282588832383e-07</v>
+        <v>2.566282588832366e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.1274200545754e-07</v>
+        <v>3.127420054575398e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5662824664142e-07</v>
+        <v>2.56628246641419e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.289674374789022e-07</v>
+        <v>2.289674374789016e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.566282466414189e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.566282466414202e-07</v>
+        <v>2.56628246641419e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.59935856647653e-07</v>
+        <v>9.599358566476547e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.295996264200415e-07</v>
+        <v>9.295996264200421e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.570603761990292e-07</v>
+        <v>9.57060376199029e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.537697015147957e-06</v>
+        <v>1.537697015147958e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.53117984768457e-07</v>
+        <v>9.531179847684575e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.58311808135807e-07</v>
+        <v>9.583118081358074e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.44129506553947e-07</v>
+        <v>9.441295065539472e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.583361122172351e-07</v>
+        <v>9.583361122172361e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.512692987633778e-07</v>
+        <v>9.512692987633772e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.602068520078653e-07</v>
+        <v>9.602068520078647e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.590395806034687e-07</v>
+        <v>9.590395806034691e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.568740063111078e-07</v>
+        <v>9.56874006311108e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.34054147270983e-07</v>
+        <v>9.340541472709844e-07</v>
       </c>
       <c r="O7" t="n">
         <v>9.59294633298967e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.511596399101544e-07</v>
+        <v>9.511596399101543e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.486208250196631e-07</v>
+        <v>9.486208250196646e-07</v>
       </c>
       <c r="R7" t="n">
         <v>9.494514132968291e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.515953688165442e-07</v>
+        <v>9.515953688165437e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.55556780879121e-07</v>
+        <v>9.5555678087912e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.437446911294662e-07</v>
+        <v>9.437446911294668e-07</v>
       </c>
       <c r="V7" t="n">
         <v>1.188401598831822e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.805604472092963e-07</v>
+        <v>8.805604472092962e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.518617546578945e-07</v>
+        <v>9.518617546578951e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.540232207206381e-07</v>
+        <v>9.540232207206379e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.556093178731074e-07</v>
+        <v>9.556093178731076e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.506423708092614e-07</v>
+        <v>9.506423708092612e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.59100589482096e-07</v>
+        <v>9.59100589482097e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.483176587089332e-07</v>
+        <v>9.483176587089355e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.396989989838586e-07</v>
+        <v>9.396989989838587e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.47512544768076e-07</v>
+        <v>9.475125447680767e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.522470620717808e-06</v>
+        <v>1.522470620717807e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.464014253795325e-07</v>
+        <v>9.464014253795338e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.47852289259171e-07</v>
+        <v>9.478522892591713e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.438602793378819e-07</v>
+        <v>9.438602793378816e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.478772286293954e-07</v>
+        <v>9.478772286293958e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.458841255214967e-07</v>
+        <v>9.45884125521496e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.484059656511867e-07</v>
+        <v>9.484059656511869e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.480664365197217e-07</v>
+        <v>9.480664365197216e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.474646048146985e-07</v>
+        <v>9.474646048146987e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.409502811672629e-07</v>
+        <v>9.409502811672617e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.481327086625084e-07</v>
+        <v>9.481327086625096e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.457951822755088e-07</v>
+        <v>9.457951822755091e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.451063561775581e-07</v>
+        <v>9.451063561775571e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.453596960070386e-07</v>
+        <v>9.453596960070391e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.459314513692996e-07</v>
+        <v>9.459314513692998e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.470860822607547e-07</v>
+        <v>9.470860822607552e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.436908529961925e-07</v>
+        <v>9.436908529961935e-07</v>
       </c>
       <c r="V8" t="n">
         <v>1.180277988175575e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.256568567454658e-07</v>
+        <v>9.256568567454669e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.46032571127218e-07</v>
+        <v>9.460325711272181e-07</v>
       </c>
       <c r="Y8" t="n">
         <v>9.466384079688768e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.470780011950734e-07</v>
+        <v>9.470780011950733e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.456719657696504e-07</v>
+        <v>9.456719657696505e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.480927568531391e-07</v>
+        <v>9.480927568531396e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.537568129462708e-07</v>
+        <v>9.537568129462992e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.528349193087852e-07</v>
+        <v>9.52834919308791e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.582962903042281e-07</v>
+        <v>9.582962903043583e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.529446040640109e-06</v>
+        <v>1.52944604064024e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.538470833732638e-07</v>
+        <v>9.538470833733902e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.5336866396279e-07</v>
+        <v>9.533686639627838e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.565802990347077e-07</v>
+        <v>9.565802990347018e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.558409916193092e-07</v>
+        <v>9.558409916192897e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.549526006231541e-07</v>
+        <v>9.549526006232536e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.609405797736288e-07</v>
+        <v>9.609405797735847e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.560413026539833e-07</v>
+        <v>9.560413026540167e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.535690067793023e-07</v>
+        <v>9.535690067793208e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.601036812941229e-07</v>
+        <v>9.601036812941634e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.541728762944801e-07</v>
+        <v>9.541728762945015e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.546518858972408e-07</v>
+        <v>9.546518858973287e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.559658561556004e-07</v>
+        <v>9.559658561555983e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.549671188319218e-07</v>
+        <v>9.549671188319163e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.563503676863768e-07</v>
+        <v>9.563503676864007e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.54849422762932e-07</v>
+        <v>9.548494227629178e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.575002486241896e-07</v>
+        <v>9.57500248624193e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.188462597099243e-06</v>
+        <v>1.188462597099244e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.673713582292771e-07</v>
+        <v>9.673713582293959e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.572423744162721e-07</v>
+        <v>9.57242374416259e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.551353119702928e-07</v>
+        <v>9.551353119702598e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.545440025163827e-07</v>
+        <v>9.545440025163594e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.552996422424214e-07</v>
+        <v>9.55299642242443e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.53894219055635e-07</v>
+        <v>9.538942190556373e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.551395108142202e-06</v>
+        <v>1.551395108142444e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.673507362546165e-07</v>
+        <v>9.673507362546171e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.205694558144786e-06</v>
+        <v>1.205694558144787e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.67358270152074e-07</v>
+        <v>9.673582701520078e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.019627565958988e-07</v>
+        <v>4.019627565964637e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.864764622463104e-07</v>
+        <v>1.864764622462621e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.713157515621826e-06</v>
+        <v>1.713157515621692e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>6.414329904029694e-07</v>
+        <v>6.414329904028623e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.679586387265675e-07</v>
+        <v>4.679586387265096e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.059890833501662e-07</v>
+        <v>3.059890833503301e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.288831034373146e-06</v>
+        <v>1.288831034373289e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.039832184960944e-06</v>
+        <v>1.039832184960887e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>7.309994905225524e-07</v>
+        <v>7.309994905225542e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.234787272310063e-06</v>
+        <v>2.234787272310384e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>9.419293251952603e-07</v>
+        <v>9.419293251952106e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.832015717080628e-07</v>
+        <v>3.832015717080123e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.123170153571213e-06</v>
+        <v>2.123170153571115e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.946210359279904e-07</v>
+        <v>4.94621035927876e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>6.328488337575645e-07</v>
+        <v>6.328488337575212e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.004125093726999e-06</v>
+        <v>1.004125093726884e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>8.085234292586535e-07</v>
+        <v>8.085234292582678e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.531063254174175e-07</v>
+        <v>9.531063254173631e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>7.28448310925249e-07</v>
+        <v>7.284483109251556e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37407295094924e-06</v>
+        <v>1.374072950949201e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>4.300510963602747e-07</v>
+        <v>4.300510963602678e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.133275351594468e-06</v>
+        <v>4.133275351594343e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.4001486181728e-06</v>
+        <v>1.400148618172712e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.975145081407194e-07</v>
+        <v>7.975145081409919e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.847324677872111e-07</v>
+        <v>5.847324677871157e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.480781581390093e-07</v>
+        <v>8.480781581388889e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.949909263028457e-07</v>
+        <v>4.949909263029193e-07</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.005628314539926e-07</v>
+        <v>1.005628314542865e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.166788588873589e-07</v>
+        <v>1.166788588872558e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.059329497510107e-07</v>
+        <v>1.059329497512499e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.421811480616731e-07</v>
+        <v>1.421811480616993e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.355011270793553e-07</v>
+        <v>1.355011270794402e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.350334423463982e-07</v>
+        <v>1.35033442346847e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.123170153571213e-06</v>
+        <v>1.08312952068207e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.156559747497276e-07</v>
+        <v>1.15655974750032e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.138560224640496e-07</v>
+        <v>1.138560224644244e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.3788569688839e-08</v>
+        <v>9.378856968902548e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.178010972223468e-07</v>
+        <v>1.178010972226179e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.282771332166416e-07</v>
+        <v>1.282771332166432e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.350402166985389e-07</v>
+        <v>1.350402166989789e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>9.694786960398602e-08</v>
+        <v>9.694786960397388e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.686093301208288e-07</v>
+        <v>1.686093301211832e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.992252216830055e-08</v>
+        <v>9.992252216823514e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.350334423461445e-07</v>
+        <v>1.350334423466811e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.710408777084996e-07</v>
+        <v>1.710408777084092e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.656995643570595e-07</v>
+        <v>2.656995643569522e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.123693740871272e-07</v>
+        <v>3.123693740872291e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.865049256822446e-07</v>
+        <v>1.865049256823538e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>3.263724221964661e-07</v>
+        <v>3.263724221965226e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>3.268400826992446e-07</v>
+        <v>3.268400826994021e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.123170153571213e-06</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.464793278399405e-07</v>
+        <v>3.464793278402173e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.50852234841167e-07</v>
+        <v>3.508522348413243e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.263724221964661e-07</v>
+        <v>3.263724221965226e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.995022817279967e-07</v>
+        <v>3.995022817279969e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.897920841599135e-07</v>
+        <v>2.897920841602855e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.263723979668457e-07</v>
+        <v>3.263723979666437e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.591880894583331e-07</v>
+        <v>9.59188089458248e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.647110934573831e-07</v>
+        <v>9.647110934572864e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.327240218005627e-07</v>
+        <v>9.327240218007571e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.538554872918703e-06</v>
+        <v>1.538554872918943e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.588272926973706e-07</v>
+        <v>9.588272926972988e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.615005216917315e-07</v>
+        <v>9.615005216916929e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.429413663143451e-07</v>
+        <v>9.429413663144013e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.471439471405388e-07</v>
+        <v>9.471439471406535e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.521341112178104e-07</v>
+        <v>9.521341112179137e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.171639322374984e-07</v>
+        <v>9.171639322375965e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.457339114377217e-07</v>
+        <v>9.457339114376709e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.604406375530237e-07</v>
+        <v>9.6044063755299e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.219457990646675e-07</v>
+        <v>9.219457990646586e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.567012491577134e-07</v>
+        <v>9.567012491577508e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.538364219851022e-07</v>
+        <v>9.538364219852107e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.463209228273845e-07</v>
+        <v>9.463209228272945e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.522844327961644e-07</v>
+        <v>9.522844327963663e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.43831487409373e-07</v>
+        <v>9.438314874093371e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.529233368043408e-07</v>
+        <v>9.529233368043546e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.370786453600665e-07</v>
+        <v>9.370786453602277e-07</v>
       </c>
       <c r="V7" t="n">
         <v>1.196940437404668e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.789003079257268e-07</v>
+        <v>8.789003079256905e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.388699696231162e-07</v>
+        <v>9.388699696232047e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.511433968963639e-07</v>
+        <v>9.511433968964339e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.545192161809317e-07</v>
+        <v>9.54519216180833e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.501612755016043e-07</v>
+        <v>9.501612755015862e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.585113112824373e-07</v>
+        <v>9.585113112823329e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.500393546937968e-07</v>
+        <v>9.500393546938182e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.516304454766047e-07</v>
+        <v>9.516304454766412e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.425375969316985e-07</v>
+        <v>9.425375969317388e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.523603692693984e-06</v>
+        <v>1.523603692694146e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.499654614448031e-07</v>
+        <v>9.499654614448854e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.507033697458212e-07</v>
+        <v>9.507033697458035e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.45470529976558e-07</v>
+        <v>9.454705299765355e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.466434102298412e-07</v>
+        <v>9.466434102298985e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.480289877390402e-07</v>
+        <v>9.480289877390466e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.381019960625177e-07</v>
+        <v>9.381019960626638e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.4620215052626e-07</v>
+        <v>9.462021505262514e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.504214619016129e-07</v>
+        <v>9.50421461901581e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.39440862228432e-07</v>
+        <v>9.394408622284605e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.493238977800729e-07</v>
+        <v>9.493238977802031e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.484994018897371e-07</v>
+        <v>9.48499401889862e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.463937960807326e-07</v>
+        <v>9.463937960808059e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.481084747976445e-07</v>
+        <v>9.481084747976297e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.456456065631218e-07</v>
+        <v>9.456456065630776e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.482814820885021e-07</v>
+        <v>9.482814820883316e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.437229228484041e-07</v>
+        <v>9.437229228484943e-07</v>
       </c>
       <c r="V8" t="n">
         <v>1.184479444264763e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.271227035175074e-07</v>
+        <v>9.271227035176221e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.442801068888811e-07</v>
+        <v>9.442801068888266e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.477574929652128e-07</v>
+        <v>9.477574929652382e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.487021920438365e-07</v>
+        <v>9.487021920438376e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.474749548729608e-07</v>
+        <v>9.474749548729307e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.498688245763773e-07</v>
+        <v>9.498688245763501e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.481929141404043e-07</v>
+        <v>9.481929141404041e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.486309445187955e-07</v>
+        <v>9.486309445187952e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.497572295030935e-07</v>
+        <v>9.497572295030931e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.525467384133827e-06</v>
+        <v>1.525467384133826e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.483460676358443e-07</v>
+        <v>9.483460676358439e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.49769502250883e-07</v>
+        <v>9.497695022508824e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.516632748863583e-07</v>
+        <v>9.516632748863576e-07</v>
       </c>
       <c r="I2" t="n">
         <v>9.491102818461446e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.497817477470139e-07</v>
+        <v>9.497817477470145e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.492477573980195e-07</v>
+        <v>9.492477573980186e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.486943955470751e-07</v>
+        <v>9.486943955470749e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.488663016666014e-07</v>
+        <v>9.488663016666009e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.501767280190069e-07</v>
+        <v>9.501767280190066e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.486218821531677e-07</v>
+        <v>9.486218821531675e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.49056220517543e-07</v>
+        <v>9.490562205175428e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.487630161859659e-07</v>
+        <v>9.487630161859658e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.491027170761439e-07</v>
+        <v>9.491027170761441e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.504732582519899e-07</v>
+        <v>9.504732582519897e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.487105375856907e-07</v>
+        <v>9.487105375856895e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.484892593019654e-07</v>
+        <v>9.484892593019658e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.184422454989713e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.579309800076433e-07</v>
+        <v>9.579309800076429e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.508883008474001e-07</v>
+        <v>9.508883008474007e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.488888439388873e-07</v>
+        <v>9.488888439388872e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.493109617350582e-07</v>
+        <v>9.493109617350579e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.520089568356723e-07</v>
+        <v>9.52008956835672e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.480280957530803e-07</v>
+        <v>9.480280957530799e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.548739928450563e-06</v>
+        <v>1.548739928450561e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.62646621526191e-07</v>
+        <v>9.626466215261914e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.201058378802613e-06</v>
+        <v>1.201058378802612e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.626364896994771e-07</v>
+        <v>9.626364896994769e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.690273618839116e-07</v>
+        <v>1.690273618839118e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.885236930297573e-07</v>
+        <v>2.885236930297572e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.631419388670115e-07</v>
+        <v>5.63141938867011e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.60993789075686e-07</v>
+        <v>2.609937890756857e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.198096452793724e-07</v>
+        <v>2.198096452793723e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.034251819540907e-07</v>
+        <v>5.034251819540923e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.119802935460144e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.17753641081683e-07</v>
+        <v>4.177536410816832e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.340002036054961e-07</v>
+        <v>5.340002036054951e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.24847427710308e-07</v>
+        <v>4.248474277103081e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.807602661284223e-07</v>
+        <v>2.807602661284213e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.384503223730033e-07</v>
+        <v>3.38450322373003e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>6.579262924825272e-07</v>
+        <v>6.57926292482527e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64734206882762e-07</v>
+        <v>2.647342068827624e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.684528291125255e-07</v>
+        <v>3.684528291125262e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.00832898139432e-07</v>
+        <v>3.008328981394323e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>4.226013723932643e-07</v>
+        <v>4.226013723932637e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>6.452623076050482e-07</v>
+        <v>6.452623076050489e-07</v>
       </c>
       <c r="T4" t="n">
         <v>3.092771468218102e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.403525159282198e-07</v>
+        <v>2.403525159282199e-07</v>
       </c>
       <c r="V4" t="n">
         <v>5.140158139491605e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.484100435332542e-06</v>
+        <v>2.48410043533254e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>8.279976959267671e-07</v>
+        <v>8.279976959267694e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.518611402875786e-07</v>
+        <v>3.518611402875801e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.152638739754879e-07</v>
+        <v>4.152638739754872e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.138459125724533e-06</v>
+        <v>1.138459125724535e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.435037671664373e-07</v>
+        <v>1.435037671664374e-07</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.749514696235477e-08</v>
+        <v>8.749514696235485e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.002003226853733e-07</v>
+        <v>1.002003226853734e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.17287148773975e-08</v>
+        <v>9.172871487739817e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.203052193030354e-07</v>
+        <v>1.203052193030351e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.151396562967791e-07</v>
+        <v>1.151396562967783e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.146702787110337e-07</v>
+        <v>1.146702787110331e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>6.579262924825272e-07</v>
+        <v>9.36050052859924e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>9.939392529222776e-08</v>
+        <v>9.939392529222694e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.797492112276555e-08</v>
+        <v>9.797492112276547e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.215461335060575e-08</v>
+        <v>8.215461335060688e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.009774646538179e-07</v>
+        <v>1.009774646538182e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09892632902625e-07</v>
+        <v>1.098926329026247e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14675619329964e-07</v>
+        <v>1.146756193299636e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>8.464526812838592e-08</v>
+        <v>8.464526812838541e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.409560081682115e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.699035494404707e-08</v>
+        <v>8.699035494404728e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.146702787110484e-07</v>
+        <v>1.146702787110477e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.430569761033796e-07</v>
+        <v>1.430569761033793e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.259287888741344e-07</v>
+        <v>2.259287888741342e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="E6" t="n">
         <v>2.644756045966001e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.605181698714037e-07</v>
+        <v>1.605181698714045e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.760413880900695e-07</v>
+        <v>2.760413880900702e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.765107500629268e-07</v>
+        <v>2.765107500629262e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>6.579262924825272e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.926486378533716e-07</v>
+        <v>2.926486378533719e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.962604297444752e-07</v>
+        <v>2.962604297444753e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.760413880900695e-07</v>
+        <v>2.760413880900702e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="V6" t="n">
         <v>3.369931328749322e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.458279469490483e-07</v>
+        <v>2.458279469490485e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.760413724771949e-07</v>
+        <v>2.760413724771957e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5658,82 +5658,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.597891221703562e-07</v>
+        <v>9.597891221703555e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.572611554990336e-07</v>
+        <v>9.572611554990332e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.506701455229447e-07</v>
+        <v>9.50670145522944e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.543844868518506e-06</v>
+        <v>1.543844868518507e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.589541888243874e-07</v>
+        <v>9.589541888243872e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.504165307099605e-07</v>
+        <v>9.504165307099608e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.396614969897714e-07</v>
+        <v>9.396614969897717e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.544749910411331e-07</v>
+        <v>9.544749910411325e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.504832847591534e-07</v>
+        <v>9.504832847591539e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.536416434966823e-07</v>
+        <v>9.536416434966816e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.568423902447452e-07</v>
+        <v>9.568423902447448e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.559144368240346e-07</v>
+        <v>9.559144368240344e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.481518469864692e-07</v>
+        <v>9.481518469864694e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.572312237325192e-07</v>
+        <v>9.57231223732519e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.546373458533855e-07</v>
+        <v>9.546373458533863e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.564780426107767e-07</v>
+        <v>9.564780426107771e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.54536065689787e-07</v>
+        <v>9.545360656897872e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.462736734170921e-07</v>
+        <v>9.462736734170918e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.568048894526241e-07</v>
+        <v>9.568048894526243e-07</v>
       </c>
       <c r="U7" t="n">
         <v>9.580505370327762e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18907379894774e-06</v>
+        <v>1.189073798947739e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>9.023379860344074e-07</v>
+        <v>9.023379860344065e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.440269587950615e-07</v>
+        <v>9.440269587950613e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.557156618074106e-07</v>
+        <v>9.557156618074104e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.531481996879007e-07</v>
+        <v>9.531481996879003e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.373102304773337e-07</v>
+        <v>9.37310230477333e-07</v>
       </c>
       <c r="AB7" t="n">
         <v>9.607990173038567e-07</v>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.468973528406323e-07</v>
+        <v>9.46897352840632e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.461851503274202e-07</v>
+        <v>9.461851503274199e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.44312504768295e-07</v>
+        <v>9.443125047682942e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.523240116265111e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.466706090028816e-07</v>
+        <v>9.466706090028813e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.442093819679546e-07</v>
+        <v>9.442093819679544e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.412095799864845e-07</v>
+        <v>9.412095799864842e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.453967739474456e-07</v>
+        <v>9.453967739474452e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.442473907557577e-07</v>
+        <v>9.44247390755758e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.451550737108727e-07</v>
+        <v>9.451550737108729e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.460580618304728e-07</v>
+        <v>9.460580618304725e-07</v>
       </c>
       <c r="M8" t="n">
         <v>9.458077461863633e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.435861694247714e-07</v>
+        <v>9.435861694247705e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.4616246891264e-07</v>
+        <v>9.461624689126406e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.454165845758119e-07</v>
+        <v>9.454165845758126e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.459609031348008e-07</v>
+        <v>9.459609031348009e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.454169983372152e-07</v>
+        <v>9.454169983372151e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.43028124698302e-07</v>
+        <v>9.43028124698303e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.460571408891649e-07</v>
+        <v>9.460571408891653e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.464026362240527e-07</v>
+        <v>9.464026362240528e-07</v>
       </c>
       <c r="V8" t="n">
         <v>1.178969432963156e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.304949686801068e-07</v>
+        <v>9.304949686801063e-07</v>
       </c>
       <c r="X8" t="n">
         <v>9.424209049808347e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.457398451926262e-07</v>
+        <v>9.457398451926269e-07</v>
       </c>
       <c r="Z8" t="n">
         <v>9.449937595424046e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.404854281795977e-07</v>
+        <v>9.404854281795975e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.471920399573966e-07</v>
+        <v>9.471920399573963e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.464069985295841e-07</v>
+        <v>9.464069985295835e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.46553123272474e-07</v>
+        <v>9.46553123272473e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.477637336875647e-07</v>
+        <v>9.477637336875637e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.524412841264466e-06</v>
+        <v>1.524412841264463e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.465998065774078e-07</v>
+        <v>9.465998065774068e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.473960336667903e-07</v>
+        <v>9.473960336667889e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.493823143921195e-07</v>
+        <v>9.493823143921188e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.47124484979542e-07</v>
+        <v>9.47124484979541e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.477300000912184e-07</v>
+        <v>9.477300000912176e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.470168530373438e-07</v>
+        <v>9.470168530373436e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.46745244980902e-07</v>
+        <v>9.467452449809012e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.472686678213323e-07</v>
+        <v>9.472686678213322e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.480886923966837e-07</v>
+        <v>9.480886923966824e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.466532146817096e-07</v>
+        <v>9.466532146817089e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.467733111103066e-07</v>
+        <v>9.467733111103057e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.466824857583581e-07</v>
+        <v>9.466824857583576e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.468820936567749e-07</v>
+        <v>9.468820936567739e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.479810770726605e-07</v>
+        <v>9.479810770726597e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.470725413553621e-07</v>
+        <v>9.470725413553619e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.472565365886029e-07</v>
+        <v>9.472565365886033e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.183675716216522e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.54152486616245e-07</v>
+        <v>9.541524866162448e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.491222973418635e-07</v>
+        <v>9.491222973418629e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.46733636265511e-07</v>
+        <v>9.467336362655101e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.470481214866997e-07</v>
+        <v>9.47048121486699e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.500577245441589e-07</v>
+        <v>9.500577245441591e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.46509173407984e-07</v>
+        <v>9.465091734079829e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.547817888617247e-06</v>
+        <v>1.547817888617246e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.608485010467677e-07</v>
+        <v>9.608485010467669e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.199591936059883e-06</v>
+        <v>1.199591936059882e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.607871503781e-07</v>
+        <v>9.607871503780992e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6166,55 +6166,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.781947923177225e-07</v>
+        <v>1.781947923177244e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.268122426796047e-07</v>
+        <v>2.268122426796049e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.294770925960041e-07</v>
+        <v>5.294770925960026e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.22914248347903e-07</v>
+        <v>2.229142483479048e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.420819268899774e-07</v>
+        <v>2.420819268899776e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.993862599914423e-07</v>
+        <v>3.99386259991443e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.891802791246139e-07</v>
+        <v>9.891802791246133e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.789254703721836e-07</v>
+        <v>3.78925470372183e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.829442695543785e-07</v>
+        <v>4.829442695543782e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.37075712463263e-07</v>
+        <v>3.370757124632627e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.580085839668738e-07</v>
+        <v>2.580085839668735e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0547396642237e-07</v>
+        <v>4.054739664223703e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>6.056478728152423e-07</v>
+        <v>6.056478728152435e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.328424210643891e-07</v>
+        <v>2.328424210643887e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.602087286914427e-07</v>
+        <v>2.60208728691443e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.500858044085537e-07</v>
+        <v>2.500858044085536e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>3.20585120249297e-07</v>
+        <v>3.205851202492958e-07</v>
       </c>
       <c r="S4" t="n">
         <v>5.305001337337907e-07</v>
@@ -6223,28 +6223,28 @@
         <v>3.603645615994447e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>3.699901397941746e-07</v>
+        <v>3.699901397941751e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.795227937722839e-07</v>
+        <v>6.795227937722841e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.060226937662058e-06</v>
+        <v>2.060226937662062e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>8.309490439119206e-07</v>
+        <v>8.309490439119201e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.697807367798155e-07</v>
+        <v>2.697807367798159e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.147338685762079e-07</v>
+        <v>3.14733868576207e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>1.110968758297235e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.243118483734959e-07</v>
+        <v>2.243118483734955e-07</v>
       </c>
     </row>
     <row r="5">
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.439030996540548e-08</v>
+        <v>8.439030996540632e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.620137243441694e-08</v>
+        <v>9.620137243441705e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.832594503420128e-08</v>
+        <v>8.832594503420083e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.148914083008297e-07</v>
+        <v>1.148914083008299e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="J5" t="n">
         <v>1.101320712235225e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.096530206694325e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>6.056478728152425e-07</v>
+        <v>9.007019349870346e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>9.545172440965521e-08</v>
+        <v>9.545172440965332e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.413258115055946e-08</v>
+        <v>9.413258115055783e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.942561073398235e-08</v>
+        <v>7.94256107339838e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>9.689031429078332e-08</v>
+        <v>9.689031429078283e-08</v>
       </c>
       <c r="V5" t="n">
         <v>1.054554675828876e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.096579854569718e-07</v>
+        <v>1.09657985456971e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>8.174098833160117e-08</v>
+        <v>8.174098833159975e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.340315946880597e-07</v>
+        <v>1.340315946880603e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.392104214860421e-08</v>
+        <v>8.392104214860449e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.096530206695577e-07</v>
+        <v>1.096530206695575e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.360420343800024e-07</v>
+        <v>1.360420343800014e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.073936308805065e-07</v>
+        <v>2.07393630880509e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.420177198943208e-07</v>
+        <v>2.420177198943195e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.48639540501019e-07</v>
+        <v>1.486395405010187e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.524065084281296e-07</v>
+        <v>2.524065084281294e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.528855489244215e-07</v>
+        <v>2.528855489244203e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>6.056478728152423e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.673237171080696e-07</v>
+        <v>2.673237171080689e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.705679540597631e-07</v>
+        <v>2.705679540597613e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.524065084281296e-07</v>
+        <v>2.524065084281294e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.075343503496439e-07</v>
+        <v>3.075343503496437e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.252677459681567e-07</v>
+        <v>2.252677459681568e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.524064983704569e-07</v>
+        <v>2.524064983704561e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6430,85 +6430,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.576830949020666e-07</v>
+        <v>9.57683094902066e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.568706106711059e-07</v>
+        <v>9.568706106711068e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.497839713903299e-07</v>
+        <v>9.4978397139033e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.543741273453417e-06</v>
+        <v>1.543741273453416e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.56622193311238e-07</v>
+        <v>9.566221933112372e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.518041571619158e-07</v>
+        <v>9.518041571619164e-07</v>
       </c>
       <c r="H7" t="n">
         <v>9.404413022044669e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.535420004930878e-07</v>
+        <v>9.535420004930873e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.503186713807981e-07</v>
+        <v>9.503186713807969e-07</v>
       </c>
       <c r="K7" t="n">
         <v>9.541494352359581e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.557029891586687e-07</v>
+        <v>9.557029891586679e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.527146310831441e-07</v>
+        <v>9.527146310831434e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.478258627338289e-07</v>
+        <v>9.478258627338286e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.562133239612738e-07</v>
+        <v>9.562133239612731e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.554933631872188e-07</v>
+        <v>9.55493363187219e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.561054442757676e-07</v>
+        <v>9.561054442757678e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.54971259158245e-07</v>
+        <v>9.549712591582452e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.483571607432732e-07</v>
+        <v>9.483571607432728e-07</v>
       </c>
       <c r="T7" t="n">
         <v>9.538370755230746e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.52672210730453e-07</v>
+        <v>9.52672210730452e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.183432229851292e-06</v>
+        <v>1.183432229851293e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>9.119941353163494e-07</v>
+        <v>9.119941353163485e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.418078864907666e-07</v>
+        <v>9.418078864907657e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.557881099280853e-07</v>
+        <v>9.557881099280859e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.538766204597184e-07</v>
+        <v>9.538766204597174e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.361813437347831e-07</v>
+        <v>9.361813437347822e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.571334295197273e-07</v>
+        <v>9.571334295197277e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6518,64 +6518,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.449946433959516e-07</v>
+        <v>9.449946433959504e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.447710852245202e-07</v>
+        <v>9.447710852245208e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.427572521830791e-07</v>
+        <v>9.427572521830792e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.522557968373519e-06</v>
+        <v>1.522557968373518e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.447047378390544e-07</v>
+        <v>9.447047378390538e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.433087431263258e-07</v>
+        <v>9.433087431263261e-07</v>
       </c>
       <c r="H8" t="n">
         <v>9.401248886347457e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.438279186929383e-07</v>
+        <v>9.438279186929385e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.429388940366253e-07</v>
+        <v>9.429388940366252e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.439966714945252e-07</v>
+        <v>9.439966714945266e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.444319354238006e-07</v>
+        <v>9.444319354238e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.435956458165352e-07</v>
+        <v>9.435956458165348e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.421912652133674e-07</v>
+        <v>9.421912652133661e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.445721090861337e-07</v>
+        <v>9.44572109086135e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.443646210681568e-07</v>
+        <v>9.443646210681564e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.445522945620843e-07</v>
+        <v>9.445522945620847e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>9.442358446175946e-07</v>
+        <v>9.442358446175954e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.42325392176787e-07</v>
+        <v>9.423253921767867e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.439102351477511e-07</v>
+        <v>9.439102351477509e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.435642131881454e-07</v>
+        <v>9.435642131881461e-07</v>
       </c>
       <c r="V8" t="n">
         <v>1.176322998393686e-06</v>
@@ -6584,19 +6584,19 @@
         <v>9.319515092690356e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.404866717898019e-07</v>
+        <v>9.40486671789801e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.444590569297583e-07</v>
+        <v>9.44459056929758e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.43903808351284e-07</v>
+        <v>9.439038083512835e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.388620041073972e-07</v>
+        <v>9.388620041073952e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.448467187737067e-07</v>
+        <v>9.44846718773706e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.570142758950603e-07</v>
+        <v>9.5701427589506e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.560813702859981e-07</v>
+        <v>9.560813702859986e-07</v>
       </c>
       <c r="D2" t="n">
         <v>9.60758945122381e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.529274550983959e-06</v>
+        <v>1.52927455098396e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.582087688423658e-07</v>
+        <v>9.58208768842366e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.559735099068201e-07</v>
+        <v>9.559735099068203e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.602450993208757e-07</v>
+        <v>9.602450993208759e-07</v>
       </c>
       <c r="I2" t="n">
         <v>9.625539772244543e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.581094909767356e-07</v>
+        <v>9.581094909767354e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.679309382502049e-07</v>
+        <v>9.679309382502047e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.565408353222845e-07</v>
+        <v>9.565408353222847e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.566245769369761e-07</v>
+        <v>9.566245769369763e-07</v>
       </c>
       <c r="N2" t="n">
         <v>9.688264932221649e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.577412567694281e-07</v>
+        <v>9.577412567694283e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.580447880323652e-07</v>
+        <v>9.580447880323654e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.600322814682388e-07</v>
+        <v>9.600322814682392e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>9.590867420472539e-07</v>
+        <v>9.590867420472545e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.588524504036399e-07</v>
+        <v>9.588524504036401e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.601203437881747e-07</v>
+        <v>9.601203437881751e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.576661617537227e-07</v>
+        <v>9.576661617537229e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.193115623182791e-06</v>
+        <v>1.19311562318279e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.680128322123703e-07</v>
+        <v>9.680128322123705e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>9.595985449328354e-07</v>
+        <v>9.595985449328352e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.588766249649721e-07</v>
+        <v>9.588766249649723e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.575098066559948e-07</v>
+        <v>9.575098066559952e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.578968307745482e-07</v>
+        <v>9.578968307745484e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.564547474973313e-07</v>
+        <v>9.564547474973315e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.552040380644787e-06</v>
+        <v>1.552040380644789e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.702578420171535e-07</v>
+        <v>9.702578420171526e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.209389027127454e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.702157165880165e-07</v>
+        <v>9.702157165880167e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0983157134887e-07</v>
+        <v>5.098315713488758e-07</v>
       </c>
       <c r="C4" t="n">
         <v>2.999209609225998e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.634919239936141e-06</v>
+        <v>1.634919239936142e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.19954565736576e-07</v>
+        <v>4.199545657365778e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.995935010964568e-07</v>
+        <v>8.995935010964557e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.551906231059601e-07</v>
+        <v>2.55190623105956e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.536931136858848e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.143297058127857e-06</v>
+        <v>2.143297058127853e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.189104539378636e-07</v>
+        <v>8.189104539378631e-07</v>
       </c>
       <c r="K4" t="n">
         <v>3.273478582942746e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.083405551463621e-07</v>
+        <v>4.083405551463758e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.462022770031434e-07</v>
+        <v>4.462022770031445e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.818960811602164e-06</v>
+        <v>3.818960811602163e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>6.759928835116501e-07</v>
+        <v>6.759928835116488e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>7.816871711561995e-07</v>
+        <v>7.816871711562002e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.360062987354596e-06</v>
+        <v>1.360062987354595e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.184466495918763e-06</v>
+        <v>1.184466495918762e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.39125415580248e-07</v>
+        <v>9.391254155802487e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.449490290799274e-06</v>
+        <v>1.449490290799272e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>7.032452927303321e-07</v>
+        <v>7.03245292730336e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.724285060500909e-07</v>
+        <v>6.724285060500882e-07</v>
       </c>
       <c r="W4" t="n">
         <v>3.538668040163699e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.281272656022118e-06</v>
+        <v>1.281272656022125e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.041473212362228e-06</v>
+        <v>1.041473212362229e-06</v>
       </c>
       <c r="Z4" t="n">
         <v>6.368614857107047e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.854201776545922e-07</v>
+        <v>7.854201776545926e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.279095697222323e-07</v>
+        <v>4.279095697222326e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.077542369402473e-07</v>
+        <v>1.077542369402475e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.251243506941094e-07</v>
+        <v>1.251243506941096e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.135422368717273e-07</v>
+        <v>1.135422368717274e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.526111284208423e-07</v>
+        <v>1.526111284208424e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.449072161601672e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="J5" t="n">
         <v>1.453863571845026e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.449072161602863e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.818960811602164e-06</v>
+        <v>1.161074416741894e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.240218697031614e-07</v>
+        <v>1.240218697031616e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.220818521606005e-07</v>
+        <v>1.220818521606006e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.004528285807884e-07</v>
+        <v>1.004528285807886e-07</v>
       </c>
       <c r="R5" t="n">
         <v>1.449072161601672e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.449072161601672e-07</v>
+        <v>1.449072161601673e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.267509173670451e-07</v>
+        <v>1.267509173670453e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.379158744214633e-07</v>
+        <v>1.379158744214632e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.449145176610461e-07</v>
+        <v>1.449145176610462e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.038579728742454e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.818092143110512e-07</v>
+        <v>1.818092143110514e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.07064101286867e-07</v>
+        <v>1.070641012868672e-07</v>
       </c>
       <c r="AA5" t="n">
         <v>1.449072161601672e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.837166095227623e-07</v>
+        <v>1.837166095227622e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.73341082009147e-07</v>
+        <v>2.733410820091471e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.210046966093472e-07</v>
+        <v>3.210046966093471e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.924600422533886e-07</v>
+        <v>1.924600422533888e-07</v>
       </c>
       <c r="G6" t="n">
         <v>3.353059310083483e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>3.357850494549781e-07</v>
+        <v>3.357850494549779e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.818960811602164e-06</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.558410008306268e-07</v>
+        <v>3.558410008306266e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.603070261945149e-07</v>
+        <v>3.603070261945148e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>3.353059310083483e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="S6" t="n">
         <v>3.35305908430643e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>4.099998742326862e-07</v>
+        <v>4.099998742326866e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.979466371911904e-07</v>
+        <v>2.979466371911907e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.353059084306431e-07</v>
+        <v>3.35305908430643e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7205,46 +7205,46 @@
         <v>9.595661470023351e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.651891001313712e-07</v>
+        <v>9.651891001313707e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.377958961949235e-07</v>
+        <v>9.377958961949238e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.544131970786181e-06</v>
+        <v>1.544131970786182e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.528190129374043e-07</v>
+        <v>9.528190129374044e-07</v>
       </c>
       <c r="G7" t="n">
         <v>9.657603313430176e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.410041927949952e-07</v>
+        <v>9.410041927949954e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.273618351555105e-07</v>
+        <v>9.273618351555106e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.534800155047105e-07</v>
+        <v>9.534800155047097e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>8.956801780051539e-07</v>
+        <v>8.956801780051535e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.624319726158051e-07</v>
+        <v>9.624319726158044e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.620442704856319e-07</v>
+        <v>9.620442704856323e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>8.902028364188041e-07</v>
+        <v>8.902028364188048e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.552248897332512e-07</v>
+        <v>9.552248897332516e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.534022282216286e-07</v>
+        <v>9.534022282216282e-07</v>
       </c>
       <c r="Q7" t="n">
         <v>9.419803008384266e-07</v>
@@ -7253,34 +7253,34 @@
         <v>9.476800831045131e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.486972153109618e-07</v>
+        <v>9.48697215310961e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.415547419483547e-07</v>
+        <v>9.415547419483544e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>9.55764797508683e-07</v>
+        <v>9.557647975086836e-07</v>
       </c>
       <c r="V7" t="n">
         <v>1.194778797121409e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.94737542914352e-07</v>
+        <v>8.947375429143521e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.445683091364676e-07</v>
+        <v>9.445683091364672e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.486940437857525e-07</v>
+        <v>9.486940437857527e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.566332277660814e-07</v>
+        <v>9.566332277660816e-07</v>
       </c>
       <c r="AA7" t="n">
         <v>9.544547645588064e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.630095125280621e-07</v>
+        <v>9.630095125280625e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.521686877954102e-07</v>
+        <v>9.5216868779541e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.537942437793485e-07</v>
+        <v>9.537942437793481e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.460078235276862e-07</v>
+        <v>9.460078235276864e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.525676199295686e-06</v>
+        <v>1.525676199295688e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.502932132413322e-07</v>
+        <v>9.502932132413324e-07</v>
       </c>
       <c r="G8" t="n">
         <v>9.539462954218751e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.469537629034487e-07</v>
+        <v>9.469537629034491e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.43055324605447e-07</v>
+        <v>9.430553246054466e-07</v>
       </c>
       <c r="J8" t="n">
         <v>9.504755264458137e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.340170306643344e-07</v>
+        <v>9.340170306643351e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.529992070096079e-07</v>
+        <v>9.529992070096077e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.529065429195372e-07</v>
+        <v>9.529065429195374e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.324203777592536e-07</v>
+        <v>9.324203777592545e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.509203827775787e-07</v>
+        <v>9.509203827775791e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.503945972442503e-07</v>
+        <v>9.503945972442506e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.471850773212447e-07</v>
+        <v>9.471850773212451e-07</v>
       </c>
       <c r="R8" t="n">
         <v>9.48832956995457e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.49061463747185e-07</v>
+        <v>9.490614637471852e-07</v>
       </c>
       <c r="T8" t="n">
         <v>9.470795089900223e-07</v>
@@ -7350,25 +7350,25 @@
         <v>9.510909475202796e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.186467921969999e-06</v>
+        <v>1.18646792197e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.336700226561859e-07</v>
+        <v>9.336700226561863e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.479288928089426e-07</v>
+        <v>9.479288928089432e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4908419525444e-07</v>
+        <v>9.490841952544398e-07</v>
       </c>
       <c r="Z8" t="n">
         <v>9.513297309571908e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.507255473740845e-07</v>
+        <v>9.50725547374084e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.531759016852425e-07</v>
+        <v>9.531759016852427e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.510964300298287e-07</v>
+        <v>9.510964300298292e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.517460342165548e-07</v>
+        <v>9.517460342165539e-07</v>
       </c>
       <c r="D2" t="n">
         <v>9.525216085506045e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.527631493855684e-06</v>
+        <v>1.527631493855686e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.509682399972457e-07</v>
+        <v>9.509682399972452e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.522390324770124e-07</v>
+        <v>9.522390324770121e-07</v>
       </c>
       <c r="H2" t="n">
         <v>9.546776285639779e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.517955377763621e-07</v>
+        <v>9.517955377763625e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.527354756615909e-07</v>
+        <v>9.527354756615911e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>9.531141292442943e-07</v>
+        <v>9.531141292442947e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.515799951336472e-07</v>
+        <v>9.515799951336474e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>9.515833030688835e-07</v>
+        <v>9.515833030688829e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>9.541774996276253e-07</v>
+        <v>9.541774996276244e-07</v>
       </c>
       <c r="O2" t="n">
         <v>9.511637759801648e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.533332526635247e-07</v>
+        <v>9.533332526635251e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.528731603347499e-07</v>
+        <v>9.528731603347501e-07</v>
       </c>
       <c r="R2" t="n">
         <v>9.521897476042047e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>9.533065146263152e-07</v>
+        <v>9.533065146263153e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>9.515560247120371e-07</v>
+        <v>9.515560247120365e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>9.514649814707506e-07</v>
+        <v>9.514649814707502e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.187700159649369e-06</v>
+        <v>1.18770015964937e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.629236984236843e-07</v>
+        <v>9.629236984236849e-07</v>
       </c>
       <c r="X2" t="n">
         <v>9.540979567132997e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.523568122060282e-07</v>
+        <v>9.52356812206028e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.521861260833492e-07</v>
+        <v>9.521861260833491e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.526922598842779e-07</v>
+        <v>9.526922598842783e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.526850124644211e-07</v>
+        <v>9.526850124644208e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7631,7 +7631,7 @@
         <v>9.654583833078531e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.550174752241664e-06</v>
+        <v>1.550174752241663e-06</v>
       </c>
       <c r="F3" t="n">
         <v>9.654583833078531e-07</v>
@@ -7646,7 +7646,7 @@
         <v>9.654583833078531e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>9.654873600468528e-07</v>
+        <v>9.65487360046853e-07</v>
       </c>
       <c r="K3" t="n">
         <v>9.654583833078531e-07</v>
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.961840131670168e-07</v>
+        <v>1.961840131670162e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.683558455560924e-07</v>
+        <v>3.683558455560929e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.741743063890796e-07</v>
+        <v>5.741743063890809e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>4.476280462518021e-07</v>
+        <v>4.476280462518033e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.785826159838263e-07</v>
+        <v>1.78582615983827e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.484810550260295e-07</v>
+        <v>4.484810550260308e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.206187749041028e-06</v>
+        <v>1.20618774904103e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>3.976581398870292e-07</v>
+        <v>3.976581398870288e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.882836468142781e-07</v>
+        <v>5.882836468142785e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.686442057609955e-07</v>
+        <v>6.686442057609948e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>3.131014956043442e-07</v>
+        <v>3.131014956043445e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.311252683181657e-07</v>
+        <v>3.311252683181648e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.001721750906125e-06</v>
+        <v>1.001721750906128e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>2.108076798108526e-07</v>
+        <v>2.108076798108561e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>7.137324743331265e-07</v>
+        <v>7.137324743331249e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.143873178491752e-07</v>
+        <v>6.143873178491756e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>5.091720853573938e-07</v>
+        <v>5.091720853573949e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>6.83433267088361e-07</v>
+        <v>6.834332670883613e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.309146311895389e-07</v>
+        <v>3.309146311895381e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.865810176324311e-07</v>
+        <v>2.865810176324319e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>5.686356668389863e-07</v>
+        <v>5.686356668389859e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.20378110233277e-06</v>
+        <v>3.203781102332767e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>9.60229841744908e-07</v>
+        <v>9.602298417449067e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.203372742994521e-07</v>
+        <v>5.203372742994516e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.357645509342332e-07</v>
+        <v>4.357645509342336e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.087267354605677e-07</v>
+        <v>6.087267354605685e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.470454245034388e-07</v>
+        <v>6.470454245034401e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.26186768551734e-08</v>
+        <v>9.261867685517409e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.064337998938116e-07</v>
+        <v>1.064337998938117e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.722209698056778e-08</v>
+        <v>9.722209698056758e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.282950969301677e-07</v>
+        <v>1.282950969301672e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.226419816737188e-07</v>
+        <v>1.226419816737184e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558398e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.221678776559979e-07</v>
+        <v>1.22167877655999e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001721750906125e-06</v>
+        <v>9.926230353853699e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.055569541460821e-07</v>
+        <v>1.055569541460816e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.040139831868101e-07</v>
+        <v>1.040139831868106e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.681158449345971e-08</v>
+        <v>8.681158449345991e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.074655207452961e-07</v>
+        <v>1.074655207452964e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.169370771584172e-07</v>
+        <v>1.169370771584173e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.221736848320312e-07</v>
+        <v>1.221736848320321e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>8.951982740781684e-08</v>
+        <v>8.951982740781654e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.510693423876842e-07</v>
+        <v>1.510693423876835e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.206978528691345e-08</v>
+        <v>9.206978528691453e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.221678776558387e-07</v>
+        <v>1.221678776558397e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.530344886747722e-07</v>
+        <v>1.530344886747726e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7889,82 +7889,82 @@
         <v>2.295293158867037e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.685469828252327e-07</v>
+        <v>2.685469828252314e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.633197030131818e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.802540429227602e-07</v>
+        <v>2.802540429227615e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.8072813122963e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.802540272117514e-07</v>
+        <v>2.802540272117513e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.001721750906125e-06</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.970641510441386e-07</v>
+        <v>2.970641510441391e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.007200611476609e-07</v>
+        <v>3.007200611476606e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.802540429227602e-07</v>
+        <v>2.802540429227615e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.41943310793619e-07</v>
+        <v>3.419433107936191e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.496715431387364e-07</v>
+        <v>2.496715431387363e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.802540272117511e-07</v>
+        <v>2.802540272117512e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.619650658729641e-07</v>
+        <v>9.619650658729645e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.582055823616734e-07</v>
+        <v>9.582055823616732e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.536710464901561e-07</v>
+        <v>9.536710464901564e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.540936994326941e-06</v>
+        <v>1.54093699432694e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.627831344987528e-07</v>
+        <v>9.627831344987526e-07</v>
       </c>
       <c r="G7" t="n">
         <v>9.551732545357159e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.412068346046533e-07</v>
+        <v>9.412068346046534e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.579381565400632e-07</v>
+        <v>9.579381565400628e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.525023266490512e-07</v>
+        <v>9.525023266490514e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.501786884459984e-07</v>
+        <v>9.501786884459986e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.591283094008003e-07</v>
+        <v>9.591283094007996e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.591911234625352e-07</v>
+        <v>9.591911234625358e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>9.438806550797284e-07</v>
+        <v>9.438806550797278e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.615601583664122e-07</v>
+        <v>9.615601583664126e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.486245595786872e-07</v>
+        <v>9.486245595786874e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.515763819858776e-07</v>
+        <v>9.515763819858781e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.556537691926374e-07</v>
+        <v>9.556537691926381e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.488683086890725e-07</v>
+        <v>9.488683086890723e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.593308856501604e-07</v>
+        <v>9.593308856501598e-07</v>
       </c>
       <c r="U7" t="n">
         <v>9.598025984624652e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.190847610784517e-06</v>
+        <v>1.190847610784518e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.921886375061972e-07</v>
+        <v>8.921886375061954e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>9.444172989538618e-07</v>
+        <v>9.444172989538611e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.545717660303395e-07</v>
+        <v>9.545717660303401e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.554933409712484e-07</v>
+        <v>9.554933409712488e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.525848161516729e-07</v>
+        <v>9.525848161516737e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.527168120317222e-07</v>
+        <v>9.527168120317224e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.495069594644128e-07</v>
+        <v>9.495069594644126e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.48445986672737e-07</v>
+        <v>9.484459866727373e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.471583327345381e-07</v>
+        <v>9.471583327345388e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.523428284565498e-06</v>
+        <v>1.5234282845655e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.497509932635925e-07</v>
+        <v>9.497509932635927e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.475592661089289e-07</v>
+        <v>9.475592661089296e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.436430966189235e-07</v>
+        <v>9.436430966189229e-07</v>
       </c>
       <c r="I8" t="n">
         <v>9.483738106314783e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.468272440847436e-07</v>
+        <v>9.468272440847444e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.461618193886532e-07</v>
+        <v>9.461618193886525e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.486997913331897e-07</v>
+        <v>9.486997913331895e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.487316798666919e-07</v>
+        <v>9.487316798666917e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.443595645196892e-07</v>
+        <v>9.44359564519688e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.493900712089029e-07</v>
+        <v>9.493900712089037e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>9.456738092205432e-07</v>
+        <v>9.456738092205426e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.465568054939374e-07</v>
+        <v>9.465568054939392e-07</v>
       </c>
       <c r="R8" t="n">
         <v>9.477286169363306e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>9.457579778053391e-07</v>
+        <v>9.457579778053393e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>9.487679937506107e-07</v>
+        <v>9.487679937506095e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>9.488915813421827e-07</v>
+        <v>9.488915813421816e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.181649714736588e-06</v>
+        <v>1.181649714736589e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>9.295857305871049e-07</v>
+        <v>9.295857305871057e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>9.445241962782765e-07</v>
+        <v>9.445241962782758e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.474033666511699e-07</v>
+        <v>9.474033666511687e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.476520000634898e-07</v>
+        <v>9.476520000634889e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.468347458025917e-07</v>
+        <v>9.468347458025922e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.468875569288027e-07</v>
+        <v>9.468875569288031e-07</v>
       </c>
     </row>
   </sheetData>
